--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4631391.509495049</v>
+        <v>4598370.498471132</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6238836.090644618</v>
+        <v>6236284.68276388</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6238836.090644618</v>
+        <v>6236284.68276388</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40338124.03991321</v>
+        <v>40333163.28208415</v>
       </c>
     </row>
   </sheetData>
@@ -654,55 +654,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>387.539806015207</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
-        <v>403.3312416337499</v>
+        <v>132.9824038734354</v>
       </c>
       <c r="H2" t="n">
-        <v>3.645548150763602</v>
+        <v>403.6455481507636</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>284.5709631262702</v>
+        <v>701.7515999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>661.794582914573</v>
+        <v>661.7945829145729</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>444.1353373590281</v>
       </c>
       <c r="M2" t="n">
-        <v>471.2428539591572</v>
+        <v>125.1662680216332</v>
       </c>
       <c r="N2" t="n">
-        <v>716</v>
+        <v>20.54997779210248</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>655.0089394376664</v>
       </c>
       <c r="Q2" t="n">
-        <v>701.7515999999999</v>
+        <v>226.9532944749972</v>
       </c>
       <c r="R2" t="n">
-        <v>224.1106691800533</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>85.13771554101635</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -745,13 +745,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>53.70931374554584</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -787,16 +787,16 @@
         <v>62.32899996461128</v>
       </c>
       <c r="T3" t="n">
-        <v>4.438765217513833</v>
+        <v>404.4387652175138</v>
       </c>
       <c r="U3" t="n">
         <v>400.1953597601868</v>
       </c>
       <c r="V3" t="n">
-        <v>46.7563108294236</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -854,13 +854,13 @@
         <v>213.4277280134412</v>
       </c>
       <c r="P4" t="n">
-        <v>19.88211893349766</v>
+        <v>264.3294710987693</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>73.56008729129394</v>
       </c>
       <c r="R4" t="n">
-        <v>318.0074394565609</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -900,31 +900,31 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>175.2189770207482</v>
+        <v>403.3312416337499</v>
       </c>
       <c r="H5" t="n">
         <v>3.645548150763602</v>
       </c>
       <c r="I5" t="n">
-        <v>133.6527576726344</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>701.7515999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>391.4802718050363</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>516.6465398266698</v>
+        <v>125.1662680216332</v>
       </c>
       <c r="N5" t="n">
         <v>20.54997779210248</v>
@@ -939,25 +939,25 @@
         <v>226.9532944749972</v>
       </c>
       <c r="R5" t="n">
-        <v>224.1106691800533</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>85.13771554101635</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8101947938906</v>
+        <v>314.4613570335762</v>
       </c>
       <c r="U5" t="n">
         <v>249.1872060963493</v>
       </c>
       <c r="V5" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>103.3443791976733</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.1177972923792</v>
@@ -1027,7 +1027,7 @@
         <v>4.438765217513833</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1953597601867614</v>
+        <v>400.1953597601868</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>84.30795674020085</v>
       </c>
     </row>
     <row r="7">
@@ -1088,16 +1088,16 @@
         <v>141.934288386439</v>
       </c>
       <c r="O7" t="n">
-        <v>213.4277280134412</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>264.3294710987693</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>73.56008729128719</v>
+        <v>233.3098469469375</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>318.0074394565609</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>182.2268911268484</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>404.3632896068686</v>
@@ -1143,7 +1143,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.331241633749869</v>
+        <v>403.3312416337499</v>
       </c>
       <c r="H8" t="n">
         <v>3.645548150763602</v>
@@ -1155,10 +1155,10 @@
         <v>284.5709631262702</v>
       </c>
       <c r="K8" t="n">
-        <v>661.794582914573</v>
+        <v>159.9075217440926</v>
       </c>
       <c r="L8" t="n">
-        <v>648.7533869346732</v>
+        <v>648.7533869346734</v>
       </c>
       <c r="M8" t="n">
         <v>125.1662680216332</v>
@@ -1167,7 +1167,7 @@
         <v>20.54997779210248</v>
       </c>
       <c r="O8" t="n">
-        <v>212.5625872980843</v>
+        <v>714.4496484685648</v>
       </c>
       <c r="P8" t="n">
         <v>655.0089394376664</v>
@@ -1176,13 +1176,13 @@
         <v>226.9532944749972</v>
       </c>
       <c r="R8" t="n">
-        <v>224.1106691800533</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>485.1377155410163</v>
+        <v>85.13771554101635</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8101947938906</v>
+        <v>580.8085993609418</v>
       </c>
       <c r="U8" t="n">
         <v>249.1872060963493</v>
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>149.9373040781138</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>47.68908699157674</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>73.56008729128607</v>
+        <v>73.56008729128426</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1374,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>196.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>196.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>195.3312416337499</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>195.6455481507636</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>16.11066918005326</v>
       </c>
       <c r="S11" t="n">
-        <v>237.6757937588244</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>376.8101947938905</v>
+        <v>193.6647399398262</v>
       </c>
       <c r="U11" t="n">
-        <v>441.1872060963494</v>
+        <v>441.1872060963493</v>
       </c>
       <c r="V11" t="n">
         <v>421.8510241668239</v>
@@ -1434,7 +1434,7 @@
         <v>384.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>303.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1462,10 +1462,10 @@
         <v>117.5115358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>121.743518136724</v>
+        <v>121.9660871864211</v>
       </c>
       <c r="I12" t="n">
-        <v>1.276385891348532</v>
+        <v>1.276385891348539</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>325.1177972923793</v>
+        <v>325.1177972923792</v>
       </c>
       <c r="S12" t="n">
         <v>254.3289999646113</v>
@@ -1513,7 +1513,7 @@
         <v>211.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>191.3913927661343</v>
+        <v>191.1688237164373</v>
       </c>
     </row>
     <row r="13">
@@ -1529,19 +1529,19 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>77.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>72.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>66.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>27.93358330561882</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>19.07165069178255</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>263.9052128576553</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.207845194782304</v>
+        <v>1.207845194782294</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>135.5832480974447</v>
+        <v>6.0185182917428</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>202.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>196.3632896068686</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>15.11066918005326</v>
+        <v>16.11066918005326</v>
       </c>
       <c r="S14" t="n">
-        <v>276.1377155410163</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>375.8101947938905</v>
+        <v>376.8101947938906</v>
       </c>
       <c r="U14" t="n">
-        <v>440.1872060963494</v>
+        <v>441.1872060963493</v>
       </c>
       <c r="V14" t="n">
-        <v>420.8510241668239</v>
+        <v>421.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>429.3734759809475</v>
+        <v>430.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>383.2818334606677</v>
+        <v>384.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>302.3174326828064</v>
+        <v>303.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175.5565566463266</v>
+        <v>176.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>152.0999124455193</v>
+        <v>153.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>138.9376868977026</v>
+        <v>139.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>133.6720972219126</v>
+        <v>134.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>130.6362423378769</v>
+        <v>131.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>116.5115358750273</v>
+        <v>117.5115358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>120.9660871864211</v>
+        <v>121.9660871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2763858913485322</v>
+        <v>1.053816841666313</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>324.1177972923793</v>
+        <v>325.1177972923792</v>
       </c>
       <c r="S15" t="n">
-        <v>253.3289999646113</v>
+        <v>254.3289999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>195.4387652175138</v>
+        <v>196.4387652175138</v>
       </c>
       <c r="U15" t="n">
-        <v>191.1953597601868</v>
+        <v>192.1953597601868</v>
       </c>
       <c r="V15" t="n">
-        <v>205.5106671915202</v>
+        <v>206.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>223.3731429098285</v>
+        <v>224.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>210.8627394453875</v>
+        <v>211.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>190.3913927661343</v>
+        <v>191.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23.24630994142384</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>18.07165069178255</v>
+        <v>19.07165069178257</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>244.8335621658728</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>150.0422993749866</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2078451947823037</v>
+        <v>1.207845194782294</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>17.37280983870968</v>
+        <v>18.37280983870968</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>78.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1854,10 +1854,10 @@
         <v>99.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>98.33124163374988</v>
+        <v>98.33124163374987</v>
       </c>
       <c r="H17" t="n">
-        <v>98.29671039044959</v>
+        <v>98.6455481507636</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>180.1377155410164</v>
+        <v>180.1377155410163</v>
       </c>
       <c r="T17" t="n">
-        <v>279.8101947938905</v>
+        <v>279.8101947938906</v>
       </c>
       <c r="U17" t="n">
-        <v>344.1872060963494</v>
+        <v>343.8383683360354</v>
       </c>
       <c r="V17" t="n">
         <v>324.8510241668239</v>
@@ -1933,7 +1933,7 @@
         <v>34.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>20.51153587502734</v>
+        <v>20.51153587502733</v>
       </c>
       <c r="H18" t="n">
         <v>24.96608718642113</v>
@@ -1966,16 +1966,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>228.1177972923793</v>
+        <v>228.1177972923792</v>
       </c>
       <c r="S18" t="n">
         <v>157.3289999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>237.0128099240158</v>
+        <v>99.43876521751383</v>
       </c>
       <c r="U18" t="n">
-        <v>95.19535976018675</v>
+        <v>232.7694044666889</v>
       </c>
       <c r="V18" t="n">
         <v>109.5106671915202</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>90.12920192827097</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>185.6683655009105</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>236.934288386439</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>308.4277280134412</v>
+        <v>26.1729034167461</v>
       </c>
       <c r="P19" t="n">
         <v>359.3294710987693</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.85402546984321</v>
+        <v>404.833266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>413.0074394565609</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2085,16 +2085,16 @@
         <v>105.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>99.01445184655462</v>
+        <v>99.36328960686865</v>
       </c>
       <c r="F20" t="n">
         <v>99.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>98.33124163374987</v>
+        <v>97.98240387343586</v>
       </c>
       <c r="H20" t="n">
-        <v>98.6455481507636</v>
+        <v>98.64554815076359</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>180.1377155410163</v>
+        <v>180.1377155410164</v>
       </c>
       <c r="T20" t="n">
-        <v>279.8101947938906</v>
+        <v>279.8101947938905</v>
       </c>
       <c r="U20" t="n">
-        <v>344.1872060963493</v>
+        <v>344.1872060963494</v>
       </c>
       <c r="V20" t="n">
         <v>324.8510241668239</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79.55655664632661</v>
+        <v>217.1306013528287</v>
       </c>
       <c r="C21" t="n">
         <v>56.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>180.5117316042046</v>
+        <v>42.93768689770263</v>
       </c>
       <c r="E21" t="n">
         <v>37.67209722191262</v>
@@ -2170,7 +2170,7 @@
         <v>34.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>20.51153587502733</v>
+        <v>20.51153587502734</v>
       </c>
       <c r="H21" t="n">
         <v>24.96608718642113</v>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>228.1177972923792</v>
+        <v>228.1177972923793</v>
       </c>
       <c r="S21" t="n">
         <v>157.3289999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>99.43876521751383</v>
+        <v>99.43876521751382</v>
       </c>
       <c r="U21" t="n">
-        <v>95.19535976018676</v>
+        <v>95.19535976018675</v>
       </c>
       <c r="V21" t="n">
         <v>109.5106671915202</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>26.1729034167461</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>359.3294710987693</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7888777807023</v>
+        <v>180.1377155410163</v>
       </c>
       <c r="T23" t="n">
         <v>279.8101947938906</v>
@@ -2373,7 +2373,7 @@
         <v>344.1872060963493</v>
       </c>
       <c r="V23" t="n">
-        <v>324.8510241668239</v>
+        <v>324.50218640651</v>
       </c>
       <c r="W23" t="n">
         <v>333.3734759809475</v>
@@ -2401,7 +2401,7 @@
         <v>42.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>175.2461419284146</v>
+        <v>37.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>34.63624233787687</v>
@@ -2413,7 +2413,7 @@
         <v>24.96608718642113</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>137.574044706502</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2550,22 +2550,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>152.3312416337499</v>
       </c>
       <c r="H26" t="n">
         <v>152.6455481507636</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>215.9009128093692</v>
+        <v>234.1377155410164</v>
       </c>
       <c r="T26" t="n">
-        <v>333.8101947938906</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>398.1872060963493</v>
+        <v>324.9805165374304</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2644,10 +2644,10 @@
         <v>88.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.967439903099941</v>
+        <v>74.51153587502735</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>78.96608718642113</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>282.1177972923792</v>
+        <v>132.6076141340307</v>
       </c>
       <c r="S27" t="n">
         <v>211.3289999646113</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>136.7938989979225</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>413.3294710987693</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>76.9456901807182</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2793,16 +2793,16 @@
         <v>198.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>159.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>153.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>153.8896287080119</v>
+        <v>21.99559505914182</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>152.3312416337499</v>
       </c>
       <c r="H29" t="n">
         <v>152.6455481507636</v>
@@ -2841,13 +2841,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>333.8101947938905</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>398.1872060963494</v>
       </c>
       <c r="V29" t="n">
-        <v>332.7780204524637</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>341.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>260.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2875,10 +2875,10 @@
         <v>96.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>91.67209722191262</v>
+        <v>30.79815640144095</v>
       </c>
       <c r="F30" t="n">
-        <v>88.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>74.51153587502735</v>
@@ -2923,13 +2923,13 @@
         <v>153.4387652175138</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>149.1953597601868</v>
       </c>
       <c r="V30" t="n">
         <v>163.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>181.0583195116667</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>168.8627394453875</v>
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>19.52071620934228</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>239.6683655009105</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>290.934288386439</v>
+        <v>91.29010367109379</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>458.833266425598</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3078,10 +3078,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>333.8101947938906</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>281.4548389148639</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>378.8510241668239</v>
@@ -3090,7 +3090,7 @@
         <v>387.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>341.2818334606677</v>
+        <v>214.3705306241352</v>
       </c>
       <c r="Y32" t="n">
         <v>260.3174326828064</v>
@@ -3118,7 +3118,7 @@
         <v>88.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>74.51153587502733</v>
+        <v>74.51153587502735</v>
       </c>
       <c r="H33" t="n">
         <v>78.96608718642113</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>282.1177972923792</v>
+        <v>282.1177972923793</v>
       </c>
       <c r="S33" t="n">
         <v>211.3289999646113</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>83.11593064013098</v>
+        <v>83.11593064013087</v>
       </c>
       <c r="R34" t="n">
         <v>467.0074394565609</v>
@@ -3261,22 +3261,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>43.29331935002761</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>152.3312416337499</v>
       </c>
       <c r="H35" t="n">
         <v>152.6455481507636</v>
@@ -3312,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>128.8092907641003</v>
+        <v>234.1377155410164</v>
       </c>
       <c r="T35" t="n">
-        <v>333.8101947938906</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>398.1872060963494</v>
       </c>
       <c r="V35" t="n">
-        <v>378.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>387.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>341.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>260.3174326828064</v>
@@ -3349,16 +3349,16 @@
         <v>96.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>91.67209722191262</v>
+        <v>30.79815640144095</v>
       </c>
       <c r="F36" t="n">
-        <v>88.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>74.51153587502735</v>
       </c>
       <c r="H36" t="n">
-        <v>3.967439903099941</v>
+        <v>78.96608718642113</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>282.1177972923792</v>
+        <v>282.1177972923793</v>
       </c>
       <c r="S36" t="n">
         <v>211.3289999646113</v>
@@ -3419,19 +3419,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>21.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>34.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>29.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>23.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>15.31290494868404</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3461,16 +3461,16 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>91.29010367109379</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>458.833266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>244.5637870781816</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>108.0422993749866</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>36.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3501,22 +3501,22 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>90.61199660343148</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>152.3312416337499</v>
       </c>
       <c r="H38" t="n">
-        <v>152.6455481507636</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>234.1377155410164</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>398.1872060963494</v>
+        <v>58.18457246008683</v>
       </c>
       <c r="V38" t="n">
         <v>378.8510241668239</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>282.1177972923793</v>
+        <v>282.1177972923792</v>
       </c>
       <c r="S39" t="n">
         <v>211.3289999646113</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.75159962293595</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -3695,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>362.4277280134412</v>
       </c>
       <c r="P40" t="n">
-        <v>413.3294710987693</v>
+        <v>187.6956420832506</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>108.0422993749866</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>384.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>352.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>313.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>306.6455481507636</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>36.65275767263435</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>127.1106691800533</v>
       </c>
       <c r="S41" t="n">
-        <v>190.6299070227527</v>
+        <v>388.1377155410163</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>227.2987159427096</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3814,16 +3814,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>287.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>94.22874778503757</v>
+        <v>264.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>245.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>232.9660871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>46.97526509047959</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>244.633960103832</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>307.4387652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>303.1953597601868</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>317.5106671915202</v>
@@ -3883,7 +3883,7 @@
         <v>322.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>302.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
         <v>73.74780318363172</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -3975,25 +3975,25 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>352.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>313.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>308.3632896068686</v>
+        <v>232.6452206719432</v>
       </c>
       <c r="F44" t="n">
-        <v>308.8896287080119</v>
+        <v>307.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>307.3312416337499</v>
+        <v>306.3312416337499</v>
       </c>
       <c r="H44" t="n">
-        <v>307.6455481507636</v>
+        <v>306.6455481507636</v>
       </c>
       <c r="I44" t="n">
-        <v>37.65275767263435</v>
+        <v>36.65275767263435</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,16 +4020,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>128.1106691800533</v>
+        <v>127.1106691800533</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>74.09566504791809</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>246.689220953385</v>
+        <v>40.5736137647779</v>
       </c>
       <c r="C45" t="n">
-        <v>265.0999124455193</v>
+        <v>264.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>251.9376868977026</v>
+        <v>250.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>246.6720972219126</v>
+        <v>245.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>243.6362423378769</v>
+        <v>242.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>228.5115358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>232.9660871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>112.2763858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,22 +4096,22 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>47.97526509047957</v>
+        <v>46.97526509047957</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>366.3289999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>308.4387652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>317.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>73.74780318363172</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>72.76770318363172</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>942.1723657396341</v>
+        <v>1477.173539719115</v>
       </c>
       <c r="C2" t="n">
-        <v>892.1980442820644</v>
+        <v>1427.199218261545</v>
       </c>
       <c r="D2" t="n">
-        <v>881.7544526256505</v>
+        <v>1012.715222564727</v>
       </c>
       <c r="E2" t="n">
-        <v>473.3066853459852</v>
+        <v>1008.307859325466</v>
       </c>
       <c r="F2" t="n">
-        <v>468.3676664490035</v>
+        <v>599.3284363880799</v>
       </c>
       <c r="G2" t="n">
-        <v>60.96237186945819</v>
+        <v>465.0027759098623</v>
       </c>
       <c r="H2" t="n">
         <v>57.28</v>
@@ -4321,52 +4321,52 @@
         <v>57.28</v>
       </c>
       <c r="J2" t="n">
-        <v>478.6745827007371</v>
+        <v>57.28</v>
       </c>
       <c r="K2" t="n">
-        <v>519.0352060193503</v>
+        <v>97.64062331861315</v>
       </c>
       <c r="L2" t="n">
-        <v>1227.87520601935</v>
+        <v>357.859070430706</v>
       </c>
       <c r="M2" t="n">
-        <v>1460.712323232323</v>
+        <v>940.2684966714805</v>
       </c>
       <c r="N2" t="n">
-        <v>1446.32</v>
+        <v>1628.350943346124</v>
       </c>
       <c r="O2" t="n">
-        <v>2155.16</v>
+        <v>2337.190943346125</v>
       </c>
       <c r="P2" t="n">
-        <v>2864</v>
+        <v>2384.405751994947</v>
       </c>
       <c r="Q2" t="n">
         <v>2864</v>
       </c>
       <c r="R2" t="n">
-        <v>2637.625586686815</v>
+        <v>2864</v>
       </c>
       <c r="S2" t="n">
-        <v>2551.627894221142</v>
+        <v>2778.002307534327</v>
       </c>
       <c r="T2" t="n">
-        <v>2364.950929782869</v>
+        <v>2591.325343096054</v>
       </c>
       <c r="U2" t="n">
-        <v>2113.246681200697</v>
+        <v>2339.621094513882</v>
       </c>
       <c r="V2" t="n">
-        <v>1881.073929517037</v>
+        <v>2107.448342830222</v>
       </c>
       <c r="W2" t="n">
-        <v>1640.292640647393</v>
+        <v>1866.667053960578</v>
       </c>
       <c r="X2" t="n">
-        <v>1446.068566444698</v>
+        <v>1672.442979757883</v>
       </c>
       <c r="Y2" t="n">
-        <v>1333.626715249944</v>
+        <v>1560.001128563129</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>422.0273863086054</v>
+        <v>454.5987435186088</v>
       </c>
       <c r="C3" t="n">
-        <v>57.28</v>
+        <v>454.5987435186088</v>
       </c>
       <c r="D3" t="n">
-        <v>57.28</v>
+        <v>454.5987435186088</v>
       </c>
       <c r="E3" t="n">
-        <v>57.28</v>
+        <v>454.5987435186088</v>
       </c>
       <c r="F3" t="n">
-        <v>57.28</v>
+        <v>111.5318320662079</v>
       </c>
       <c r="G3" t="n">
-        <v>57.28</v>
+        <v>111.5318320662079</v>
       </c>
       <c r="H3" t="n">
         <v>57.28</v>
@@ -4430,22 +4430,22 @@
         <v>1334.781243038242</v>
       </c>
       <c r="T3" t="n">
-        <v>1330.29764180843</v>
+        <v>926.257237768026</v>
       </c>
       <c r="U3" t="n">
-        <v>926.0599046769283</v>
+        <v>522.0195006365242</v>
       </c>
       <c r="V3" t="n">
-        <v>878.8313078795308</v>
+        <v>507.3622610491301</v>
       </c>
       <c r="W3" t="n">
-        <v>442.0907594857645</v>
+        <v>474.662116695768</v>
       </c>
       <c r="X3" t="n">
-        <v>422.0273863086054</v>
+        <v>454.5987435186088</v>
       </c>
       <c r="Y3" t="n">
-        <v>422.0273863086054</v>
+        <v>454.5987435186088</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>452.3375566050018</v>
+      </c>
+      <c r="C4" t="n">
+        <v>578.3395624234375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>578.3395624234375</v>
+      </c>
+      <c r="E4" t="n">
+        <v>578.3395624234375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>578.3395624234375</v>
+      </c>
+      <c r="G4" t="n">
+        <v>677.91925771098</v>
+      </c>
+      <c r="H4" t="n">
+        <v>849.1183235261153</v>
+      </c>
+      <c r="I4" t="n">
+        <v>849.1183235261153</v>
+      </c>
+      <c r="J4" t="n">
+        <v>849.1183235261153</v>
+      </c>
+      <c r="K4" t="n">
+        <v>849.1183235261153</v>
+      </c>
+      <c r="L4" t="n">
+        <v>849.1183235261153</v>
+      </c>
+      <c r="M4" t="n">
+        <v>757.5341159494379</v>
+      </c>
+      <c r="N4" t="n">
+        <v>614.1661478823278</v>
+      </c>
+      <c r="O4" t="n">
+        <v>398.5825842323871</v>
+      </c>
+      <c r="P4" t="n">
+        <v>131.5831184760545</v>
+      </c>
+      <c r="Q4" t="n">
         <v>57.28</v>
-      </c>
-      <c r="C4" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="D4" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="E4" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="F4" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="G4" t="n">
-        <v>210.875801952459</v>
-      </c>
-      <c r="H4" t="n">
-        <v>247.8318695113467</v>
-      </c>
-      <c r="I4" t="n">
-        <v>474.6555930375935</v>
-      </c>
-      <c r="J4" t="n">
-        <v>849.1183235261104</v>
-      </c>
-      <c r="K4" t="n">
-        <v>849.1183235261104</v>
-      </c>
-      <c r="L4" t="n">
-        <v>849.1183235261104</v>
-      </c>
-      <c r="M4" t="n">
-        <v>757.534115949433</v>
-      </c>
-      <c r="N4" t="n">
-        <v>614.166147882323</v>
-      </c>
-      <c r="O4" t="n">
-        <v>398.5825842323824</v>
-      </c>
-      <c r="P4" t="n">
-        <v>378.499635814708</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>378.499635814708</v>
       </c>
       <c r="R4" t="n">
         <v>57.28</v>
@@ -4518,13 +4518,13 @@
         <v>57.28</v>
       </c>
       <c r="W4" t="n">
-        <v>57.28</v>
+        <v>229.1709182596774</v>
       </c>
       <c r="X4" t="n">
-        <v>57.28</v>
+        <v>229.1709182596774</v>
       </c>
       <c r="Y4" t="n">
-        <v>57.28</v>
+        <v>340.5802189387097</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>442.7183183251215</v>
+        <v>1346.212769780038</v>
       </c>
       <c r="C5" t="n">
-        <v>392.7439968675519</v>
+        <v>1296.238448322468</v>
       </c>
       <c r="D5" t="n">
-        <v>382.300405211138</v>
+        <v>1285.794856666055</v>
       </c>
       <c r="E5" t="n">
-        <v>377.8930419718768</v>
+        <v>877.3470893863893</v>
       </c>
       <c r="F5" t="n">
-        <v>372.9540230748951</v>
+        <v>468.3676664490035</v>
       </c>
       <c r="G5" t="n">
-        <v>195.9651573973717</v>
+        <v>60.96237186945819</v>
       </c>
       <c r="H5" t="n">
-        <v>192.2827855279135</v>
+        <v>57.28</v>
       </c>
       <c r="I5" t="n">
         <v>57.28</v>
@@ -4561,10 +4561,10 @@
         <v>57.28</v>
       </c>
       <c r="K5" t="n">
-        <v>766.12</v>
+        <v>370.6853820151148</v>
       </c>
       <c r="L5" t="n">
-        <v>1474.96</v>
+        <v>1079.525382015115</v>
       </c>
       <c r="M5" t="n">
         <v>1661.934808255889</v>
@@ -4582,28 +4582,28 @@
         <v>2864</v>
       </c>
       <c r="R5" t="n">
-        <v>2637.625586686815</v>
+        <v>2864</v>
       </c>
       <c r="S5" t="n">
-        <v>2551.627894221142</v>
+        <v>2778.002307534327</v>
       </c>
       <c r="T5" t="n">
-        <v>2364.950929782869</v>
+        <v>2460.364573156977</v>
       </c>
       <c r="U5" t="n">
-        <v>2113.246681200697</v>
+        <v>2208.660324574806</v>
       </c>
       <c r="V5" t="n">
-        <v>1477.033525476633</v>
+        <v>1976.487572891145</v>
       </c>
       <c r="W5" t="n">
-        <v>1236.252236606989</v>
+        <v>1735.706284021501</v>
       </c>
       <c r="X5" t="n">
-        <v>637.9877583638901</v>
+        <v>1541.482209818807</v>
       </c>
       <c r="Y5" t="n">
-        <v>525.5459071691362</v>
+        <v>1429.040358624053</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>754.8656405248639</v>
+        <v>773.4795952961838</v>
       </c>
       <c r="C6" t="n">
-        <v>754.8656405248639</v>
+        <v>408.7322089875785</v>
       </c>
       <c r="D6" t="n">
-        <v>403.4134315372855</v>
+        <v>57.28</v>
       </c>
       <c r="E6" t="n">
         <v>57.28</v>
@@ -4658,31 +4658,31 @@
         <v>1532.202250368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1427.813988552704</v>
+        <v>1532.202250368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1293.35156704525</v>
+        <v>1397.739828861082</v>
       </c>
       <c r="S6" t="n">
-        <v>1230.392981222411</v>
+        <v>1334.781243038242</v>
       </c>
       <c r="T6" t="n">
-        <v>1225.909379992599</v>
+        <v>1330.29764180843</v>
       </c>
       <c r="U6" t="n">
-        <v>1225.712046901501</v>
+        <v>926.0599046769283</v>
       </c>
       <c r="V6" t="n">
-        <v>1211.054807314107</v>
+        <v>911.4026650895343</v>
       </c>
       <c r="W6" t="n">
-        <v>1178.354662960744</v>
+        <v>878.7025207361721</v>
       </c>
       <c r="X6" t="n">
-        <v>1158.291289783585</v>
+        <v>858.6391475590129</v>
       </c>
       <c r="Y6" t="n">
-        <v>754.8656405248639</v>
+        <v>773.4795952961838</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>645.0312091477208</v>
+        <v>208.3107910241935</v>
       </c>
       <c r="C7" t="n">
-        <v>645.0312091477208</v>
+        <v>208.3107910241935</v>
       </c>
       <c r="D7" t="n">
-        <v>645.0312091477208</v>
+        <v>208.3107910241935</v>
       </c>
       <c r="E7" t="n">
-        <v>645.0312091477208</v>
+        <v>208.3107910241935</v>
       </c>
       <c r="F7" t="n">
-        <v>645.0312091477208</v>
+        <v>332.671763616129</v>
       </c>
       <c r="G7" t="n">
-        <v>645.0312091477208</v>
+        <v>474.6555930375923</v>
       </c>
       <c r="H7" t="n">
-        <v>816.2302749628561</v>
+        <v>474.6555930375923</v>
       </c>
       <c r="I7" t="n">
-        <v>844.2962334350967</v>
+        <v>474.6555930375923</v>
       </c>
       <c r="J7" t="n">
-        <v>844.2962334350967</v>
+        <v>849.1183235261092</v>
       </c>
       <c r="K7" t="n">
-        <v>844.2962334350967</v>
+        <v>849.1183235261092</v>
       </c>
       <c r="L7" t="n">
-        <v>849.1183235261085</v>
+        <v>849.1183235261092</v>
       </c>
       <c r="M7" t="n">
-        <v>757.5341159494311</v>
+        <v>757.5341159494318</v>
       </c>
       <c r="N7" t="n">
-        <v>614.166147882321</v>
+        <v>614.1661478823216</v>
       </c>
       <c r="O7" t="n">
-        <v>398.5825842323803</v>
+        <v>614.1661478823216</v>
       </c>
       <c r="P7" t="n">
-        <v>131.5831184760477</v>
+        <v>614.1661478823216</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.28</v>
+        <v>378.499635814708</v>
       </c>
       <c r="R7" t="n">
         <v>57.28</v>
       </c>
       <c r="S7" t="n">
-        <v>97.82812361876331</v>
+        <v>57.28</v>
       </c>
       <c r="T7" t="n">
-        <v>286.7123568759288</v>
+        <v>57.28</v>
       </c>
       <c r="U7" t="n">
-        <v>533.2738714814286</v>
+        <v>57.28</v>
       </c>
       <c r="V7" t="n">
-        <v>533.2738714814286</v>
+        <v>57.28</v>
       </c>
       <c r="W7" t="n">
-        <v>533.2738714814286</v>
+        <v>57.28</v>
       </c>
       <c r="X7" t="n">
-        <v>533.2738714814286</v>
+        <v>208.3107910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>533.2738714814286</v>
+        <v>208.3107910241935</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>846.758722365526</v>
+        <v>1077.175151267548</v>
       </c>
       <c r="C8" t="n">
-        <v>796.7844009079563</v>
+        <v>1027.200829809978</v>
       </c>
       <c r="D8" t="n">
-        <v>612.71683411316</v>
+        <v>1016.757238153564</v>
       </c>
       <c r="E8" t="n">
-        <v>204.2690668334946</v>
+        <v>608.3094708738987</v>
       </c>
       <c r="F8" t="n">
-        <v>199.330047936513</v>
+        <v>603.370451976917</v>
       </c>
       <c r="G8" t="n">
         <v>195.9651573973717</v>
@@ -4798,16 +4798,16 @@
         <v>478.6745827007371</v>
       </c>
       <c r="K8" t="n">
-        <v>519.0352060193503</v>
+        <v>1025.99183346428</v>
       </c>
       <c r="L8" t="n">
-        <v>572.5687545701852</v>
+        <v>1079.525382015115</v>
       </c>
       <c r="M8" t="n">
-        <v>1154.97818081096</v>
+        <v>1661.934808255889</v>
       </c>
       <c r="N8" t="n">
-        <v>1843.060627485604</v>
+        <v>2350.017254930533</v>
       </c>
       <c r="O8" t="n">
         <v>2337.190943346125</v>
@@ -4819,28 +4819,28 @@
         <v>2864</v>
       </c>
       <c r="R8" t="n">
-        <v>2637.625586686815</v>
+        <v>2864</v>
       </c>
       <c r="S8" t="n">
-        <v>2147.587490180738</v>
+        <v>2778.002307534327</v>
       </c>
       <c r="T8" t="n">
-        <v>1960.910525742465</v>
+        <v>2191.326954644487</v>
       </c>
       <c r="U8" t="n">
-        <v>1709.206277160294</v>
+        <v>1939.622706062316</v>
       </c>
       <c r="V8" t="n">
-        <v>1477.033525476633</v>
+        <v>1707.449954378655</v>
       </c>
       <c r="W8" t="n">
-        <v>1236.252236606989</v>
+        <v>1466.668665509011</v>
       </c>
       <c r="X8" t="n">
-        <v>1042.028162404295</v>
+        <v>1272.444591306316</v>
       </c>
       <c r="Y8" t="n">
-        <v>929.5863112095407</v>
+        <v>1160.002740111562</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>470.198181249592</v>
+        <v>1111.227729298292</v>
       </c>
       <c r="C9" t="n">
-        <v>105.4507949409866</v>
+        <v>746.4803429896865</v>
       </c>
       <c r="D9" t="n">
-        <v>57.28</v>
+        <v>746.4803429896865</v>
       </c>
       <c r="E9" t="n">
-        <v>57.28</v>
+        <v>400.3469114524009</v>
       </c>
       <c r="F9" t="n">
         <v>57.28</v>
@@ -4916,10 +4916,10 @@
         <v>1282.742924776576</v>
       </c>
       <c r="X9" t="n">
-        <v>858.6391475590128</v>
+        <v>1262.679551599417</v>
       </c>
       <c r="Y9" t="n">
-        <v>858.6391475590128</v>
+        <v>1262.679551599417</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="C10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="D10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="E10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="F10" t="n">
-        <v>474.6555930375905</v>
+        <v>370.525205849101</v>
       </c>
       <c r="G10" t="n">
-        <v>474.6555930375905</v>
+        <v>370.525205849101</v>
       </c>
       <c r="H10" t="n">
-        <v>474.6555930375905</v>
+        <v>370.525205849101</v>
       </c>
       <c r="I10" t="n">
-        <v>474.6555930375905</v>
+        <v>370.525205849101</v>
       </c>
       <c r="J10" t="n">
-        <v>849.1183235261074</v>
+        <v>744.987936337618</v>
       </c>
       <c r="K10" t="n">
-        <v>849.1183235261074</v>
+        <v>844.2962334350937</v>
       </c>
       <c r="L10" t="n">
-        <v>849.1183235261074</v>
+        <v>849.1183235261054</v>
       </c>
       <c r="M10" t="n">
-        <v>757.53411594943</v>
+        <v>757.534115949428</v>
       </c>
       <c r="N10" t="n">
-        <v>614.1661478823198</v>
+        <v>614.166147882318</v>
       </c>
       <c r="O10" t="n">
-        <v>398.5825842323792</v>
+        <v>398.5825842323774</v>
       </c>
       <c r="P10" t="n">
-        <v>131.5831184760465</v>
+        <v>131.5831184760447</v>
       </c>
       <c r="Q10" t="n">
-        <v>131.5831184760465</v>
+        <v>131.5831184760447</v>
       </c>
       <c r="R10" t="n">
         <v>57.28</v>
       </c>
       <c r="S10" t="n">
-        <v>97.82812361876331</v>
+        <v>57.28</v>
       </c>
       <c r="T10" t="n">
-        <v>228.0940784320908</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="U10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="V10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="W10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="X10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
       <c r="Y10" t="n">
-        <v>474.6555930375905</v>
+        <v>246.1642332571655</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255.6267571786552</v>
+        <v>651.084463123763</v>
       </c>
       <c r="C11" t="n">
-        <v>255.6267571786552</v>
+        <v>651.084463123763</v>
       </c>
       <c r="D11" t="n">
-        <v>255.6267571786552</v>
+        <v>651.084463123763</v>
       </c>
       <c r="E11" t="n">
-        <v>57.28</v>
+        <v>651.084463123763</v>
       </c>
       <c r="F11" t="n">
-        <v>57.28</v>
+        <v>452.2060502873874</v>
       </c>
       <c r="G11" t="n">
-        <v>57.28</v>
+        <v>254.9017658088521</v>
       </c>
       <c r="H11" t="n">
         <v>57.28</v>
@@ -5041,16 +5041,16 @@
         <v>1259.808893439666</v>
       </c>
       <c r="M11" t="n">
-        <v>1629.432241571597</v>
+        <v>1844.734288098249</v>
       </c>
       <c r="N11" t="n">
-        <v>2317.927763557416</v>
+        <v>2533.229810084068</v>
       </c>
       <c r="O11" t="n">
-        <v>2319.462611573537</v>
+        <v>2534.764658100189</v>
       </c>
       <c r="P11" t="n">
-        <v>2379.843761530247</v>
+        <v>2595.145808056899</v>
       </c>
       <c r="Q11" t="n">
         <v>2864</v>
@@ -5059,25 +5059,25 @@
         <v>2847.726596787825</v>
       </c>
       <c r="S11" t="n">
-        <v>2607.650037435477</v>
+        <v>2847.726596787825</v>
       </c>
       <c r="T11" t="n">
-        <v>2227.03367905781</v>
+        <v>2652.105647353657</v>
       </c>
       <c r="U11" t="n">
-        <v>1781.390036536245</v>
+        <v>2206.462004832092</v>
       </c>
       <c r="V11" t="n">
-        <v>1355.27789091319</v>
+        <v>1780.349859209038</v>
       </c>
       <c r="W11" t="n">
-        <v>920.5572081041524</v>
+        <v>1345.6291764</v>
       </c>
       <c r="X11" t="n">
-        <v>532.3937399620638</v>
+        <v>957.4657082579109</v>
       </c>
       <c r="Y11" t="n">
-        <v>532.3937399620638</v>
+        <v>651.084463123763</v>
       </c>
     </row>
     <row r="12">
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>865.2369482890015</v>
+        <v>865.4617655109178</v>
       </c>
       <c r="C12" t="n">
-        <v>710.5905720814062</v>
+        <v>710.8153893033225</v>
       </c>
       <c r="D12" t="n">
-        <v>569.2393731948379</v>
+        <v>569.4641904167541</v>
       </c>
       <c r="E12" t="n">
-        <v>433.2069517585625</v>
+        <v>433.4317689804788</v>
       </c>
       <c r="F12" t="n">
-        <v>300.2410504071717</v>
+        <v>300.4658676290879</v>
       </c>
       <c r="G12" t="n">
-        <v>181.5425293212854</v>
+        <v>181.7673465432017</v>
       </c>
       <c r="H12" t="n">
-        <v>58.56927867812983</v>
+        <v>58.56927867812984</v>
       </c>
       <c r="I12" t="n">
         <v>57.28</v>
@@ -5120,13 +5120,13 @@
         <v>1366.324167864882</v>
       </c>
       <c r="M12" t="n">
-        <v>1715.517009607742</v>
+        <v>1542.490271678781</v>
       </c>
       <c r="N12" t="n">
-        <v>2113.42330421531</v>
+        <v>1940.396566286349</v>
       </c>
       <c r="O12" t="n">
-        <v>2612.090285899029</v>
+        <v>2439.063547970068</v>
       </c>
       <c r="P12" t="n">
         <v>2800.615512439575</v>
@@ -5156,7 +5156,7 @@
         <v>1236.901543655124</v>
       </c>
       <c r="Y12" t="n">
-        <v>1043.576904497412</v>
+        <v>1043.801721719328</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>323.8509220784397</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="C13" t="n">
-        <v>323.8509220784397</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="D13" t="n">
-        <v>245.531509901111</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="E13" t="n">
-        <v>171.8134242072155</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="F13" t="n">
-        <v>104.7600343408095</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="G13" t="n">
-        <v>76.54429362806319</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="H13" t="n">
+        <v>103.9445137149713</v>
+      </c>
+      <c r="I13" t="n">
+        <v>140.6882372412182</v>
+      </c>
+      <c r="J13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="K13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="L13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="M13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="N13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="O13" t="n">
+        <v>325.070967729735</v>
+      </c>
+      <c r="P13" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="R13" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="S13" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="T13" t="n">
         <v>57.28</v>
       </c>
-      <c r="I13" t="n">
-        <v>94.02372352624684</v>
-      </c>
-      <c r="J13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="K13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="L13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="M13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="N13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="O13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="P13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="R13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="S13" t="n">
-        <v>278.4064540147637</v>
-      </c>
-      <c r="T13" t="n">
-        <v>277.1864083634684</v>
-      </c>
       <c r="U13" t="n">
-        <v>333.6679229689682</v>
+        <v>113.7615146054998</v>
       </c>
       <c r="V13" t="n">
-        <v>342.4093158549142</v>
+        <v>122.5029074914457</v>
       </c>
       <c r="W13" t="n">
-        <v>323.8509220784397</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="X13" t="n">
-        <v>323.8509220784397</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="Y13" t="n">
-        <v>323.8509220784397</v>
+        <v>103.9445137149713</v>
       </c>
     </row>
     <row r="14">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57.28</v>
+        <v>460.0097427744631</v>
       </c>
       <c r="C14" t="n">
-        <v>57.28</v>
+        <v>460.0097427744631</v>
       </c>
       <c r="D14" t="n">
-        <v>57.28</v>
+        <v>255.6267571786552</v>
       </c>
       <c r="E14" t="n">
         <v>57.28</v>
@@ -5272,49 +5272,49 @@
         <v>484.3947465049924</v>
       </c>
       <c r="K14" t="n">
-        <v>538.0581094195653</v>
+        <v>1193.234746504992</v>
       </c>
       <c r="L14" t="n">
-        <v>1246.898109419565</v>
+        <v>1259.808893439666</v>
       </c>
       <c r="M14" t="n">
-        <v>1831.823504078149</v>
+        <v>1844.734288098249</v>
       </c>
       <c r="N14" t="n">
-        <v>2520.319026063967</v>
+        <v>2533.229810084068</v>
       </c>
       <c r="O14" t="n">
-        <v>2521.853874080088</v>
+        <v>2534.764658100189</v>
       </c>
       <c r="P14" t="n">
-        <v>2582.235024036799</v>
+        <v>2595.145808056899</v>
       </c>
       <c r="Q14" t="n">
         <v>2864</v>
       </c>
       <c r="R14" t="n">
-        <v>2848.736697797926</v>
+        <v>2847.726596787825</v>
       </c>
       <c r="S14" t="n">
-        <v>2569.80971240296</v>
+        <v>2847.726596787825</v>
       </c>
       <c r="T14" t="n">
-        <v>2190.203455035394</v>
+        <v>2467.110238410158</v>
       </c>
       <c r="U14" t="n">
-        <v>1745.56991352393</v>
+        <v>2021.466595888593</v>
       </c>
       <c r="V14" t="n">
-        <v>1320.467868910976</v>
+        <v>1595.354450265538</v>
       </c>
       <c r="W14" t="n">
-        <v>886.7572871120392</v>
+        <v>1160.6337674565</v>
       </c>
       <c r="X14" t="n">
-        <v>499.6039199800516</v>
+        <v>772.4702993144118</v>
       </c>
       <c r="Y14" t="n">
-        <v>194.2327758560047</v>
+        <v>466.0890541802639</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>858.3910584402106</v>
+        <v>865.2369482890165</v>
       </c>
       <c r="C15" t="n">
-        <v>704.7547832427164</v>
+        <v>710.5905720814212</v>
       </c>
       <c r="D15" t="n">
-        <v>564.4136853662491</v>
+        <v>569.2393731948529</v>
       </c>
       <c r="E15" t="n">
-        <v>429.3913649400747</v>
+        <v>433.2069517585775</v>
       </c>
       <c r="F15" t="n">
-        <v>297.4355645987849</v>
+        <v>300.2410504071867</v>
       </c>
       <c r="G15" t="n">
-        <v>179.7471445229997</v>
+        <v>181.5425293213005</v>
       </c>
       <c r="H15" t="n">
-        <v>57.55917766802882</v>
+        <v>58.3444614562286</v>
       </c>
       <c r="I15" t="n">
         <v>57.28</v>
       </c>
       <c r="J15" t="n">
-        <v>409.472110175299</v>
+        <v>408.482110175299</v>
       </c>
       <c r="K15" t="n">
-        <v>645.1402194010216</v>
+        <v>840.0437562696824</v>
       </c>
       <c r="L15" t="n">
-        <v>1172.410630996222</v>
+        <v>1366.324167864882</v>
       </c>
       <c r="M15" t="n">
-        <v>1522.593472739081</v>
+        <v>1542.490271678796</v>
       </c>
       <c r="N15" t="n">
-        <v>1921.489767346649</v>
+        <v>1940.396566286364</v>
       </c>
       <c r="O15" t="n">
-        <v>2421.146749030368</v>
+        <v>2439.063547970083</v>
       </c>
       <c r="P15" t="n">
-        <v>2783.688713499875</v>
+        <v>2800.61551243959</v>
       </c>
       <c r="Q15" t="n">
-        <v>2848.0632010603</v>
+        <v>2864.000000000015</v>
       </c>
       <c r="R15" t="n">
-        <v>2520.671486623553</v>
+        <v>2535.598184553167</v>
       </c>
       <c r="S15" t="n">
-        <v>2264.78360787142</v>
+        <v>2278.700204790934</v>
       </c>
       <c r="T15" t="n">
-        <v>2067.370713712316</v>
+        <v>2080.277209621728</v>
       </c>
       <c r="U15" t="n">
-        <v>1874.244087691925</v>
+        <v>1886.140482591236</v>
       </c>
       <c r="V15" t="n">
-        <v>1666.657555175238</v>
+        <v>1677.543849064448</v>
       </c>
       <c r="W15" t="n">
-        <v>1441.028117892583</v>
+        <v>1450.904310771692</v>
       </c>
       <c r="X15" t="n">
-        <v>1228.035451786131</v>
+        <v>1236.901543655139</v>
       </c>
       <c r="Y15" t="n">
-        <v>1035.72091363852</v>
+        <v>1043.576904497427</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="C16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="D16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="E16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="F16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="G16" t="n">
-        <v>75.53419261796218</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="H16" t="n">
+        <v>84.68022008690809</v>
+      </c>
+      <c r="I16" t="n">
+        <v>121.423943613155</v>
+      </c>
+      <c r="J16" t="n">
+        <v>305.8066741016718</v>
+      </c>
+      <c r="K16" t="n">
+        <v>305.8066741016718</v>
+      </c>
+      <c r="L16" t="n">
+        <v>305.8066741016718</v>
+      </c>
+      <c r="M16" t="n">
+        <v>305.8066741016718</v>
+      </c>
+      <c r="N16" t="n">
+        <v>305.8066741016718</v>
+      </c>
+      <c r="O16" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="P16" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="R16" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="S16" t="n">
+        <v>58.50004565129525</v>
+      </c>
+      <c r="T16" t="n">
         <v>57.28</v>
       </c>
-      <c r="I16" t="n">
-        <v>95.01372352624685</v>
-      </c>
-      <c r="J16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="K16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="L16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="M16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="N16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="O16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="P16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="R16" t="n">
-        <v>280.3864540147637</v>
-      </c>
-      <c r="S16" t="n">
-        <v>128.8285758582116</v>
-      </c>
-      <c r="T16" t="n">
-        <v>128.6186312170174</v>
-      </c>
       <c r="U16" t="n">
-        <v>186.0901458225171</v>
+        <v>113.7615146054998</v>
       </c>
       <c r="V16" t="n">
-        <v>195.8215387084631</v>
+        <v>122.5029074914457</v>
       </c>
       <c r="W16" t="n">
-        <v>178.2732459420897</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="X16" t="n">
-        <v>178.2732459420897</v>
+        <v>103.9445137149713</v>
       </c>
       <c r="Y16" t="n">
-        <v>99.01531377091555</v>
+        <v>103.9445137149713</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>709.4967720423472</v>
+        <v>709.8491334164017</v>
       </c>
       <c r="C17" t="n">
-        <v>563.5628546251816</v>
+        <v>563.9152159992361</v>
       </c>
       <c r="D17" t="n">
-        <v>457.1596670091717</v>
+        <v>457.5120283832263</v>
       </c>
       <c r="E17" t="n">
-        <v>356.7927078103145</v>
+        <v>357.145069184369</v>
       </c>
       <c r="F17" t="n">
-        <v>255.8940929537368</v>
+        <v>256.2464543277914</v>
       </c>
       <c r="G17" t="n">
-        <v>156.5696064549996</v>
+        <v>156.9219678290542</v>
       </c>
       <c r="H17" t="n">
         <v>57.28</v>
@@ -5509,22 +5509,22 @@
         <v>484.3947465049924</v>
       </c>
       <c r="K17" t="n">
-        <v>977.9326999783409</v>
+        <v>1193.234746504992</v>
       </c>
       <c r="L17" t="n">
-        <v>1044.506846913014</v>
+        <v>1902.074746504992</v>
       </c>
       <c r="M17" t="n">
-        <v>1629.432241571597</v>
+        <v>2487.000141163576</v>
       </c>
       <c r="N17" t="n">
-        <v>2317.927763557416</v>
+        <v>2802.084002027168</v>
       </c>
       <c r="O17" t="n">
-        <v>2319.462611573537</v>
+        <v>2803.61885004329</v>
       </c>
       <c r="P17" t="n">
-        <v>2379.843761530247</v>
+        <v>2864</v>
       </c>
       <c r="Q17" t="n">
         <v>2864</v>
@@ -5539,19 +5539,19 @@
         <v>2399.406151176862</v>
       </c>
       <c r="U17" t="n">
-        <v>2051.742306635095</v>
+        <v>2052.094668009149</v>
       </c>
       <c r="V17" t="n">
-        <v>1723.609958991838</v>
+        <v>1723.962320365893</v>
       </c>
       <c r="W17" t="n">
-        <v>1386.869074162598</v>
+        <v>1387.221435536653</v>
       </c>
       <c r="X17" t="n">
-        <v>1096.685404000308</v>
+        <v>1097.037765374362</v>
       </c>
       <c r="Y17" t="n">
-        <v>888.2839568459578</v>
+        <v>888.6363182200123</v>
       </c>
     </row>
     <row r="18">
@@ -5615,22 +5615,22 @@
         <v>1142.86205111905</v>
       </c>
       <c r="T18" t="n">
-        <v>903.4551724079231</v>
+        <v>1042.418853929642</v>
       </c>
       <c r="U18" t="n">
-        <v>807.2982433572295</v>
+        <v>807.2982433572294</v>
       </c>
       <c r="V18" t="n">
-        <v>696.6814078102394</v>
+        <v>696.6814078102393</v>
       </c>
       <c r="W18" t="n">
-        <v>568.0216674972813</v>
+        <v>568.0216674972812</v>
       </c>
       <c r="X18" t="n">
-        <v>451.9986983605262</v>
+        <v>451.9986983605261</v>
       </c>
       <c r="Y18" t="n">
-        <v>356.6538571826127</v>
+        <v>356.6538571826126</v>
       </c>
     </row>
     <row r="19">
@@ -5670,22 +5670,22 @@
         <v>1272.778061007752</v>
       </c>
       <c r="L19" t="n">
-        <v>1181.738463100407</v>
+        <v>1272.778061007752</v>
       </c>
       <c r="M19" t="n">
-        <v>994.1946595641341</v>
+        <v>1272.778061007752</v>
       </c>
       <c r="N19" t="n">
-        <v>754.867095537428</v>
+        <v>1272.778061007752</v>
       </c>
       <c r="O19" t="n">
-        <v>443.3239359278914</v>
+        <v>1246.34078482922</v>
       </c>
       <c r="P19" t="n">
-        <v>80.36487421196284</v>
+        <v>883.3817231132919</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.28</v>
+        <v>474.4592317743039</v>
       </c>
       <c r="R19" t="n">
         <v>57.28</v>
@@ -5728,10 +5728,10 @@
         <v>457.1596670091717</v>
       </c>
       <c r="E20" t="n">
-        <v>357.145069184369</v>
+        <v>356.7927078103145</v>
       </c>
       <c r="F20" t="n">
-        <v>256.2464543277914</v>
+        <v>255.8940929537368</v>
       </c>
       <c r="G20" t="n">
         <v>156.9219678290542</v>
@@ -5746,13 +5746,13 @@
         <v>484.3947465049924</v>
       </c>
       <c r="K20" t="n">
-        <v>1193.234746504992</v>
+        <v>977.9326999783409</v>
       </c>
       <c r="L20" t="n">
-        <v>1902.074746504992</v>
+        <v>1044.506846913014</v>
       </c>
       <c r="M20" t="n">
-        <v>2317.927763557416</v>
+        <v>1629.432241571597</v>
       </c>
       <c r="N20" t="n">
         <v>2317.927763557416</v>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>415.2573804757191</v>
+        <v>276.2936989539999</v>
       </c>
       <c r="C21" t="n">
-        <v>358.5908022479218</v>
+        <v>219.6271207262026</v>
       </c>
       <c r="D21" t="n">
         <v>176.2557198194323</v>
@@ -5855,19 +5855,19 @@
         <v>1042.418853929642</v>
       </c>
       <c r="U21" t="n">
-        <v>946.2619248789487</v>
+        <v>946.2619248789488</v>
       </c>
       <c r="V21" t="n">
-        <v>835.6450893319586</v>
+        <v>835.6450893319587</v>
       </c>
       <c r="W21" t="n">
-        <v>706.9853490190005</v>
+        <v>706.9853490190006</v>
       </c>
       <c r="X21" t="n">
-        <v>590.9623798822454</v>
+        <v>590.9623798822455</v>
       </c>
       <c r="Y21" t="n">
-        <v>495.6175387043319</v>
+        <v>495.617538704332</v>
       </c>
     </row>
     <row r="22">
@@ -5913,7 +5913,7 @@
         <v>1272.778061007752</v>
       </c>
       <c r="N22" t="n">
-        <v>1246.34078482922</v>
+        <v>1272.778061007752</v>
       </c>
       <c r="O22" t="n">
         <v>1246.34078482922</v>
@@ -5980,19 +5980,19 @@
         <v>57.28</v>
       </c>
       <c r="J23" t="n">
-        <v>269.092699978341</v>
+        <v>484.3947465049924</v>
       </c>
       <c r="K23" t="n">
-        <v>977.9326999783409</v>
+        <v>1193.234746504992</v>
       </c>
       <c r="L23" t="n">
-        <v>1044.506846913014</v>
+        <v>1259.808893439666</v>
       </c>
       <c r="M23" t="n">
-        <v>1629.432241571597</v>
+        <v>1259.808893439666</v>
       </c>
       <c r="N23" t="n">
-        <v>2317.927763557416</v>
+        <v>1610.622611573537</v>
       </c>
       <c r="O23" t="n">
         <v>2319.462611573537</v>
@@ -6007,13 +6007,13 @@
         <v>2864</v>
       </c>
       <c r="S23" t="n">
-        <v>2682.395072948786</v>
+        <v>2682.042711574731</v>
       </c>
       <c r="T23" t="n">
-        <v>2399.758512550916</v>
+        <v>2399.406151176862</v>
       </c>
       <c r="U23" t="n">
-        <v>2052.094668009149</v>
+        <v>2051.742306635095</v>
       </c>
       <c r="V23" t="n">
         <v>1723.962320365893</v>
@@ -6044,16 +6044,16 @@
         <v>315.2194013411515</v>
       </c>
       <c r="E24" t="n">
-        <v>138.2030963629549</v>
+        <v>277.166777884674</v>
       </c>
       <c r="F24" t="n">
-        <v>103.2169929913621</v>
+        <v>242.1806745130812</v>
       </c>
       <c r="G24" t="n">
-        <v>82.49826988527387</v>
+        <v>221.461951406993</v>
       </c>
       <c r="H24" t="n">
-        <v>57.28</v>
+        <v>196.2436815217191</v>
       </c>
       <c r="I24" t="n">
         <v>57.28</v>
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>350.5114917765409</v>
+        <v>509.8860055801649</v>
       </c>
       <c r="C26" t="n">
-        <v>350.5114917765409</v>
+        <v>509.8860055801649</v>
       </c>
       <c r="D26" t="n">
-        <v>350.5114917765409</v>
+        <v>348.9373634187004</v>
       </c>
       <c r="E26" t="n">
-        <v>350.5114917765409</v>
+        <v>348.9373634187004</v>
       </c>
       <c r="F26" t="n">
-        <v>195.0674223745087</v>
+        <v>348.9373634187004</v>
       </c>
       <c r="G26" t="n">
         <v>195.0674223745087</v>
@@ -6223,10 +6223,10 @@
         <v>95.65642019927013</v>
       </c>
       <c r="L26" t="n">
-        <v>601.5464201992701</v>
+        <v>486.1477635574163</v>
       </c>
       <c r="M26" t="n">
-        <v>1107.43642019927</v>
+        <v>992.0377635574163</v>
       </c>
       <c r="N26" t="n">
         <v>1497.927763557416</v>
@@ -6244,25 +6244,25 @@
         <v>2044</v>
       </c>
       <c r="S26" t="n">
-        <v>1825.918269889526</v>
+        <v>1807.497257029276</v>
       </c>
       <c r="T26" t="n">
-        <v>1488.736254946202</v>
+        <v>1807.497257029276</v>
       </c>
       <c r="U26" t="n">
-        <v>1086.526955858981</v>
+        <v>1479.23410901167</v>
       </c>
       <c r="V26" t="n">
-        <v>1086.526955858981</v>
+        <v>1479.23410901167</v>
       </c>
       <c r="W26" t="n">
-        <v>695.2406164842861</v>
+        <v>1087.947769636975</v>
       </c>
       <c r="X26" t="n">
-        <v>350.5114917765409</v>
+        <v>743.2186449292301</v>
       </c>
       <c r="Y26" t="n">
-        <v>350.5114917765409</v>
+        <v>743.2186449292301</v>
       </c>
     </row>
     <row r="27">
@@ -6272,46 +6272,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>436.1460391980924</v>
+        <v>587.1664262267273</v>
       </c>
       <c r="C27" t="n">
-        <v>324.9340064248405</v>
+        <v>475.9543934534754</v>
       </c>
       <c r="D27" t="n">
-        <v>227.0171509726156</v>
+        <v>378.0375380012505</v>
       </c>
       <c r="E27" t="n">
-        <v>134.4190729706837</v>
+        <v>285.4394599993186</v>
       </c>
       <c r="F27" t="n">
-        <v>44.88751505363631</v>
+        <v>195.9079020822712</v>
       </c>
       <c r="G27" t="n">
-        <v>40.88</v>
+        <v>120.6437244307284</v>
       </c>
       <c r="H27" t="n">
         <v>40.88</v>
       </c>
       <c r="I27" t="n">
-        <v>82.18637796756495</v>
+        <v>40.88</v>
       </c>
       <c r="J27" t="n">
-        <v>227.4684881428639</v>
+        <v>186.1621101752989</v>
       </c>
       <c r="K27" t="n">
-        <v>453.1101342372473</v>
+        <v>411.8037562696824</v>
       </c>
       <c r="L27" t="n">
-        <v>959.0001342372473</v>
+        <v>732.1641678648825</v>
       </c>
       <c r="M27" t="n">
-        <v>1102.272975980106</v>
+        <v>875.4370096077417</v>
       </c>
       <c r="N27" t="n">
-        <v>1294.259270587675</v>
+        <v>1315.91330421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1587.006252271393</v>
+        <v>1608.660285899029</v>
       </c>
       <c r="P27" t="n">
         <v>1938.045512439575</v>
@@ -6320,28 +6320,28 @@
         <v>2044</v>
       </c>
       <c r="R27" t="n">
-        <v>1759.032527987496</v>
+        <v>1910.052915016131</v>
       </c>
       <c r="S27" t="n">
-        <v>1545.568891659605</v>
+        <v>1696.58927868824</v>
       </c>
       <c r="T27" t="n">
-        <v>1390.580239924743</v>
+        <v>1541.600626953378</v>
       </c>
       <c r="U27" t="n">
-        <v>1239.877856328595</v>
+        <v>1390.898243357229</v>
       </c>
       <c r="V27" t="n">
-        <v>1074.71556623615</v>
+        <v>1225.735953264785</v>
       </c>
       <c r="W27" t="n">
-        <v>891.5103713777373</v>
+        <v>1042.530758406372</v>
       </c>
       <c r="X27" t="n">
-        <v>720.9419476955277</v>
+        <v>871.9623347241626</v>
       </c>
       <c r="Y27" t="n">
-        <v>571.0516519721597</v>
+        <v>722.0720390007946</v>
       </c>
     </row>
     <row r="28">
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>260.5188500324822</v>
+        <v>223.6851602855505</v>
       </c>
       <c r="C28" t="n">
-        <v>260.5188500324822</v>
+        <v>223.6851602855505</v>
       </c>
       <c r="D28" t="n">
-        <v>260.5188500324822</v>
+        <v>223.6851602855505</v>
       </c>
       <c r="E28" t="n">
-        <v>260.5188500324822</v>
+        <v>223.6851602855505</v>
       </c>
       <c r="F28" t="n">
-        <v>260.5188500324822</v>
+        <v>200.0661138534879</v>
       </c>
       <c r="G28" t="n">
-        <v>266.6046519849412</v>
+        <v>206.1519158059469</v>
       </c>
       <c r="H28" t="n">
-        <v>290.2937178000765</v>
+        <v>229.8409816210822</v>
       </c>
       <c r="I28" t="n">
-        <v>369.6074413263233</v>
+        <v>309.1547051473291</v>
       </c>
       <c r="J28" t="n">
-        <v>596.5601718148403</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="K28" t="n">
-        <v>596.5601718148403</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="L28" t="n">
-        <v>596.5601718148403</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="M28" t="n">
-        <v>596.5601718148403</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="N28" t="n">
-        <v>596.5601718148403</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="O28" t="n">
-        <v>458.3845162613832</v>
+        <v>536.1074356358459</v>
       </c>
       <c r="P28" t="n">
-        <v>40.88</v>
+        <v>118.6029193744628</v>
       </c>
       <c r="Q28" t="n">
-        <v>40.88</v>
+        <v>118.6029193744628</v>
       </c>
       <c r="R28" t="n">
         <v>40.88</v>
@@ -6405,22 +6405,22 @@
         <v>40.88</v>
       </c>
       <c r="T28" t="n">
-        <v>82.25423325716554</v>
+        <v>82.25423325716552</v>
       </c>
       <c r="U28" t="n">
         <v>181.3057478626653</v>
       </c>
       <c r="V28" t="n">
-        <v>232.6171407486113</v>
+        <v>232.6171407486112</v>
       </c>
       <c r="W28" t="n">
-        <v>256.9980590082887</v>
+        <v>256.9980590082886</v>
       </c>
       <c r="X28" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="Y28" t="n">
-        <v>260.5188500324822</v>
+        <v>223.6851602855505</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>866.8519196449372</v>
+        <v>726.5469219126443</v>
       </c>
       <c r="C29" t="n">
-        <v>666.3725476823171</v>
+        <v>526.0675499500242</v>
       </c>
       <c r="D29" t="n">
-        <v>505.4239055208527</v>
+        <v>526.0675499500242</v>
       </c>
       <c r="E29" t="n">
-        <v>350.5114917765409</v>
+        <v>371.1551362057124</v>
       </c>
       <c r="F29" t="n">
-        <v>195.0674223745087</v>
+        <v>348.9373634187004</v>
       </c>
       <c r="G29" t="n">
         <v>195.0674223745087</v>
@@ -6454,25 +6454,25 @@
         <v>40.88</v>
       </c>
       <c r="J29" t="n">
-        <v>467.9947465049924</v>
+        <v>41.99305728469727</v>
       </c>
       <c r="K29" t="n">
-        <v>925.4636166227428</v>
+        <v>547.8830572846972</v>
       </c>
       <c r="L29" t="n">
-        <v>992.0377635574163</v>
+        <v>1053.773057284697</v>
       </c>
       <c r="M29" t="n">
-        <v>1497.927763557416</v>
+        <v>1559.663057284698</v>
       </c>
       <c r="N29" t="n">
-        <v>1497.927763557416</v>
+        <v>1559.663057284698</v>
       </c>
       <c r="O29" t="n">
-        <v>1499.462611573537</v>
+        <v>1561.197905300818</v>
       </c>
       <c r="P29" t="n">
-        <v>1559.843761530247</v>
+        <v>1621.579055257529</v>
       </c>
       <c r="Q29" t="n">
         <v>2044</v>
@@ -6484,22 +6484,22 @@
         <v>2044</v>
       </c>
       <c r="T29" t="n">
-        <v>2044</v>
+        <v>1706.817985056676</v>
       </c>
       <c r="U29" t="n">
-        <v>2044</v>
+        <v>1304.608685969455</v>
       </c>
       <c r="V29" t="n">
-        <v>1707.860585401552</v>
+        <v>1304.608685969455</v>
       </c>
       <c r="W29" t="n">
-        <v>1707.860585401552</v>
+        <v>1304.608685969455</v>
       </c>
       <c r="X29" t="n">
-        <v>1363.131460693807</v>
+        <v>959.8795612617095</v>
       </c>
       <c r="Y29" t="n">
-        <v>1100.184558994002</v>
+        <v>959.8795612617095</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>587.1664262267273</v>
+        <v>436.1460391980924</v>
       </c>
       <c r="C30" t="n">
-        <v>475.9543934534754</v>
+        <v>324.9340064248405</v>
       </c>
       <c r="D30" t="n">
-        <v>378.0375380012505</v>
+        <v>227.0171509726156</v>
       </c>
       <c r="E30" t="n">
-        <v>285.4394599993186</v>
+        <v>195.9079020822712</v>
       </c>
       <c r="F30" t="n">
         <v>195.9079020822712</v>
@@ -6533,22 +6533,22 @@
         <v>82.18637796756497</v>
       </c>
       <c r="J30" t="n">
-        <v>475.9584881428639</v>
+        <v>227.4684881428639</v>
       </c>
       <c r="K30" t="n">
-        <v>701.6001342372473</v>
+        <v>453.1101342372473</v>
       </c>
       <c r="L30" t="n">
-        <v>1021.960545832447</v>
+        <v>773.4705458324474</v>
       </c>
       <c r="M30" t="n">
         <v>1165.233387575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1489.666566286349</v>
+        <v>1357.219682182875</v>
       </c>
       <c r="O30" t="n">
-        <v>1782.413547970068</v>
+        <v>1649.966663866594</v>
       </c>
       <c r="P30" t="n">
         <v>1938.045512439575</v>
@@ -6566,19 +6566,19 @@
         <v>1390.580239924743</v>
       </c>
       <c r="U30" t="n">
-        <v>1390.580239924743</v>
+        <v>1239.877856328595</v>
       </c>
       <c r="V30" t="n">
-        <v>1225.417949832298</v>
+        <v>1074.71556623615</v>
       </c>
       <c r="W30" t="n">
-        <v>1042.530758406372</v>
+        <v>891.5103713777373</v>
       </c>
       <c r="X30" t="n">
-        <v>871.9623347241626</v>
+        <v>720.9419476955277</v>
       </c>
       <c r="Y30" t="n">
-        <v>722.0720390007946</v>
+        <v>571.0516519721597</v>
       </c>
     </row>
     <row r="31">
@@ -6618,19 +6618,19 @@
         <v>596.5601718148403</v>
       </c>
       <c r="L31" t="n">
-        <v>576.8422766538885</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="M31" t="n">
-        <v>334.7530185721606</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="N31" t="n">
-        <v>40.88</v>
+        <v>504.3479458844425</v>
       </c>
       <c r="O31" t="n">
-        <v>40.88</v>
+        <v>504.3479458844425</v>
       </c>
       <c r="P31" t="n">
-        <v>40.88</v>
+        <v>504.3479458844425</v>
       </c>
       <c r="Q31" t="n">
         <v>40.88</v>
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.88</v>
+        <v>557.2204278683963</v>
       </c>
       <c r="C32" t="n">
-        <v>40.88</v>
+        <v>356.7410559057762</v>
       </c>
       <c r="D32" t="n">
-        <v>40.88</v>
+        <v>195.7924137443118</v>
       </c>
       <c r="E32" t="n">
         <v>40.88</v>
@@ -6697,19 +6697,19 @@
         <v>95.65642019927013</v>
       </c>
       <c r="L32" t="n">
-        <v>601.5464201992701</v>
+        <v>162.2305671339435</v>
       </c>
       <c r="M32" t="n">
-        <v>992.0377635574163</v>
+        <v>668.1205671339435</v>
       </c>
       <c r="N32" t="n">
-        <v>1497.927763557416</v>
+        <v>1174.010567133943</v>
       </c>
       <c r="O32" t="n">
-        <v>1499.462611573537</v>
+        <v>1175.545415150064</v>
       </c>
       <c r="P32" t="n">
-        <v>1559.843761530247</v>
+        <v>1681.435415150064</v>
       </c>
       <c r="Q32" t="n">
         <v>2044</v>
@@ -6721,22 +6721,22 @@
         <v>2044</v>
       </c>
       <c r="T32" t="n">
-        <v>1706.817985056676</v>
+        <v>2044</v>
       </c>
       <c r="U32" t="n">
-        <v>1422.520167970955</v>
+        <v>2044</v>
       </c>
       <c r="V32" t="n">
-        <v>1039.842365782244</v>
+        <v>1661.322197811289</v>
       </c>
       <c r="W32" t="n">
-        <v>648.5560264075497</v>
+        <v>1270.035858436594</v>
       </c>
       <c r="X32" t="n">
-        <v>303.8269016998045</v>
+        <v>1053.499968917266</v>
       </c>
       <c r="Y32" t="n">
-        <v>40.88</v>
+        <v>790.5530672174615</v>
       </c>
     </row>
     <row r="33">
@@ -6767,22 +6767,22 @@
         <v>40.88</v>
       </c>
       <c r="I33" t="n">
-        <v>82.18637796756495</v>
+        <v>82.18637796756497</v>
       </c>
       <c r="J33" t="n">
-        <v>359.9153722463383</v>
+        <v>227.4684881428639</v>
       </c>
       <c r="K33" t="n">
-        <v>585.5570183407217</v>
+        <v>701.6001342372474</v>
       </c>
       <c r="L33" t="n">
-        <v>905.9174299359219</v>
+        <v>1021.960545832448</v>
       </c>
       <c r="M33" t="n">
-        <v>1297.680271678781</v>
+        <v>1165.233387575307</v>
       </c>
       <c r="N33" t="n">
-        <v>1489.666566286349</v>
+        <v>1357.219682182875</v>
       </c>
       <c r="O33" t="n">
         <v>1782.413547970068</v>
@@ -6825,19 +6825,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="C34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="D34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="E34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="F34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="G34" t="n">
         <v>266.6046519849412</v>
@@ -6870,7 +6870,7 @@
         <v>596.5601718148403</v>
       </c>
       <c r="Q34" t="n">
-        <v>512.6046863197585</v>
+        <v>512.6046863197586</v>
       </c>
       <c r="R34" t="n">
         <v>40.88</v>
@@ -6879,22 +6879,22 @@
         <v>40.88</v>
       </c>
       <c r="T34" t="n">
-        <v>82.25423325716554</v>
+        <v>82.25423325716552</v>
       </c>
       <c r="U34" t="n">
         <v>181.3057478626653</v>
       </c>
       <c r="V34" t="n">
-        <v>232.6171407486113</v>
+        <v>232.6171407486112</v>
       </c>
       <c r="W34" t="n">
-        <v>256.9980590082887</v>
+        <v>256.9980590082886</v>
       </c>
       <c r="X34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="Y34" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
     </row>
     <row r="35">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>195.0674223745087</v>
+        <v>909.0084168931853</v>
       </c>
       <c r="C35" t="n">
-        <v>195.0674223745087</v>
+        <v>708.5290449305652</v>
       </c>
       <c r="D35" t="n">
-        <v>195.0674223745087</v>
+        <v>547.5804027691007</v>
       </c>
       <c r="E35" t="n">
-        <v>195.0674223745087</v>
+        <v>392.6679890247889</v>
       </c>
       <c r="F35" t="n">
-        <v>195.0674223745087</v>
+        <v>348.9373634187004</v>
       </c>
       <c r="G35" t="n">
         <v>195.0674223745087</v>
@@ -6931,13 +6931,13 @@
         <v>41.99305728469727</v>
       </c>
       <c r="K35" t="n">
-        <v>547.8830572846972</v>
+        <v>419.5736166227429</v>
       </c>
       <c r="L35" t="n">
-        <v>614.4572042193706</v>
+        <v>486.1477635574163</v>
       </c>
       <c r="M35" t="n">
-        <v>1120.347204219371</v>
+        <v>992.0377635574163</v>
       </c>
       <c r="N35" t="n">
         <v>1497.927763557416</v>
@@ -6955,25 +6955,25 @@
         <v>2044</v>
       </c>
       <c r="S35" t="n">
-        <v>1913.889605288788</v>
+        <v>1807.497257029276</v>
       </c>
       <c r="T35" t="n">
-        <v>1576.707590345464</v>
+        <v>1807.497257029276</v>
       </c>
       <c r="U35" t="n">
-        <v>1576.707590345464</v>
+        <v>1405.287957942055</v>
       </c>
       <c r="V35" t="n">
-        <v>1194.029788156753</v>
+        <v>1405.287957942055</v>
       </c>
       <c r="W35" t="n">
-        <v>802.7434487820583</v>
+        <v>1405.287957942055</v>
       </c>
       <c r="X35" t="n">
-        <v>458.0143240743132</v>
+        <v>1405.287957942055</v>
       </c>
       <c r="Y35" t="n">
-        <v>195.0674223745087</v>
+        <v>1142.34105624225</v>
       </c>
     </row>
     <row r="36">
@@ -6992,37 +6992,37 @@
         <v>227.0171509726156</v>
       </c>
       <c r="E36" t="n">
-        <v>134.4190729706837</v>
+        <v>195.9079020822712</v>
       </c>
       <c r="F36" t="n">
-        <v>44.88751505363631</v>
+        <v>195.9079020822712</v>
       </c>
       <c r="G36" t="n">
-        <v>44.88751505363631</v>
+        <v>120.6437244307284</v>
       </c>
       <c r="H36" t="n">
         <v>40.88</v>
       </c>
       <c r="I36" t="n">
-        <v>82.18637796756495</v>
+        <v>82.18637796756497</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4684881428639</v>
+        <v>359.9153722463385</v>
       </c>
       <c r="K36" t="n">
-        <v>453.1101342372473</v>
+        <v>585.5570183407219</v>
       </c>
       <c r="L36" t="n">
-        <v>773.4705458324474</v>
+        <v>905.9174299359221</v>
       </c>
       <c r="M36" t="n">
-        <v>1084.5372533625</v>
+        <v>1049.190271678781</v>
       </c>
       <c r="N36" t="n">
-        <v>1276.523547970068</v>
+        <v>1241.176566286349</v>
       </c>
       <c r="O36" t="n">
-        <v>1782.413547970068</v>
+        <v>1533.923547970068</v>
       </c>
       <c r="P36" t="n">
         <v>1938.045512439575</v>
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>187.2065740864812</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="C37" t="n">
-        <v>165.2618805025976</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="D37" t="n">
-        <v>130.3768117596123</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="E37" t="n">
-        <v>100.0930695000602</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="F37" t="n">
-        <v>76.47402306799768</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="G37" t="n">
-        <v>82.5598250204567</v>
+        <v>266.6046519849412</v>
       </c>
       <c r="H37" t="n">
-        <v>106.248890835592</v>
+        <v>290.2937178000765</v>
       </c>
       <c r="I37" t="n">
-        <v>185.5626143618388</v>
+        <v>369.6074413263233</v>
       </c>
       <c r="J37" t="n">
-        <v>412.5153448503557</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="K37" t="n">
-        <v>397.0477640941093</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="L37" t="n">
-        <v>397.0477640941093</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="M37" t="n">
-        <v>397.0477640941093</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="N37" t="n">
-        <v>397.0477640941093</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="O37" t="n">
-        <v>397.0477640941093</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="P37" t="n">
-        <v>397.0477640941093</v>
+        <v>504.3479458844425</v>
       </c>
       <c r="Q37" t="n">
-        <v>397.0477640941093</v>
+        <v>40.88</v>
       </c>
       <c r="R37" t="n">
-        <v>150.0136357323097</v>
+        <v>40.88</v>
       </c>
       <c r="S37" t="n">
         <v>40.88</v>
       </c>
       <c r="T37" t="n">
-        <v>82.25423325716554</v>
+        <v>82.25423325716552</v>
       </c>
       <c r="U37" t="n">
         <v>181.3057478626653</v>
       </c>
       <c r="V37" t="n">
-        <v>232.6171407486113</v>
+        <v>232.6171407486112</v>
       </c>
       <c r="W37" t="n">
-        <v>256.9980590082887</v>
+        <v>256.9980590082886</v>
       </c>
       <c r="X37" t="n">
-        <v>260.5188500324822</v>
+        <v>260.5188500324821</v>
       </c>
       <c r="Y37" t="n">
-        <v>223.6851602855505</v>
+        <v>260.5188500324821</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>286.5946916709041</v>
+        <v>866.5344383146203</v>
       </c>
       <c r="C38" t="n">
-        <v>286.5946916709041</v>
+        <v>666.0550663520002</v>
       </c>
       <c r="D38" t="n">
-        <v>195.0674223745087</v>
+        <v>505.1064241905357</v>
       </c>
       <c r="E38" t="n">
-        <v>195.0674223745087</v>
+        <v>350.194010446224</v>
       </c>
       <c r="F38" t="n">
-        <v>195.0674223745087</v>
+        <v>194.7499410441918</v>
       </c>
       <c r="G38" t="n">
-        <v>195.0674223745087</v>
+        <v>40.88</v>
       </c>
       <c r="H38" t="n">
         <v>40.88</v>
@@ -7165,25 +7165,25 @@
         <v>40.88</v>
       </c>
       <c r="J38" t="n">
-        <v>467.9947465049924</v>
+        <v>41.99305728469727</v>
       </c>
       <c r="K38" t="n">
-        <v>521.6581094195652</v>
+        <v>547.8830572846972</v>
       </c>
       <c r="L38" t="n">
-        <v>588.2322563542385</v>
+        <v>614.4572042193706</v>
       </c>
       <c r="M38" t="n">
-        <v>1094.122256354239</v>
+        <v>1120.347204219371</v>
       </c>
       <c r="N38" t="n">
-        <v>1600.012256354239</v>
+        <v>1497.927763557416</v>
       </c>
       <c r="O38" t="n">
-        <v>1601.547104370359</v>
+        <v>1499.462611573537</v>
       </c>
       <c r="P38" t="n">
-        <v>1661.92825432707</v>
+        <v>1559.843761530247</v>
       </c>
       <c r="Q38" t="n">
         <v>2044</v>
@@ -7192,25 +7192,25 @@
         <v>2044</v>
       </c>
       <c r="S38" t="n">
-        <v>1807.497257029276</v>
+        <v>2044</v>
       </c>
       <c r="T38" t="n">
-        <v>1807.497257029276</v>
+        <v>2044</v>
       </c>
       <c r="U38" t="n">
-        <v>1405.287957942055</v>
+        <v>1985.227704585771</v>
       </c>
       <c r="V38" t="n">
-        <v>1022.610155753344</v>
+        <v>1602.54990239706</v>
       </c>
       <c r="W38" t="n">
-        <v>631.3238163786493</v>
+        <v>1211.263563022365</v>
       </c>
       <c r="X38" t="n">
-        <v>286.5946916709041</v>
+        <v>866.5344383146203</v>
       </c>
       <c r="Y38" t="n">
-        <v>286.5946916709041</v>
+        <v>866.5344383146203</v>
       </c>
     </row>
     <row r="39">
@@ -7241,7 +7241,7 @@
         <v>40.88</v>
       </c>
       <c r="I39" t="n">
-        <v>82.18637796756497</v>
+        <v>82.18637796756495</v>
       </c>
       <c r="J39" t="n">
         <v>359.9153722463385</v>
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>231.4768302113347</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="C40" t="n">
-        <v>231.4768302113347</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="D40" t="n">
-        <v>231.4768302113347</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="E40" t="n">
-        <v>231.4768302113347</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="F40" t="n">
-        <v>231.4768302113347</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="G40" t="n">
-        <v>237.5626321637938</v>
+        <v>266.6046519849412</v>
       </c>
       <c r="H40" t="n">
-        <v>261.251697978929</v>
+        <v>290.2937178000765</v>
       </c>
       <c r="I40" t="n">
-        <v>340.5654215051759</v>
+        <v>369.6074413263233</v>
       </c>
       <c r="J40" t="n">
-        <v>567.5181519936928</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="K40" t="n">
-        <v>567.5181519936928</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="L40" t="n">
-        <v>567.5181519936928</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="M40" t="n">
-        <v>567.5181519936928</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="N40" t="n">
-        <v>567.5181519936928</v>
+        <v>596.5601718148403</v>
       </c>
       <c r="O40" t="n">
-        <v>567.5181519936928</v>
+        <v>230.4715576598491</v>
       </c>
       <c r="P40" t="n">
-        <v>150.0136357323097</v>
+        <v>40.88</v>
       </c>
       <c r="Q40" t="n">
-        <v>150.0136357323097</v>
+        <v>40.88</v>
       </c>
       <c r="R40" t="n">
-        <v>150.0136357323097</v>
+        <v>40.88</v>
       </c>
       <c r="S40" t="n">
         <v>40.88</v>
       </c>
       <c r="T40" t="n">
-        <v>82.25423325716552</v>
+        <v>82.25423325716554</v>
       </c>
       <c r="U40" t="n">
         <v>181.3057478626653</v>
       </c>
       <c r="V40" t="n">
-        <v>232.6171407486112</v>
+        <v>232.6171407486113</v>
       </c>
       <c r="W40" t="n">
-        <v>256.9980590082886</v>
+        <v>256.9980590082887</v>
       </c>
       <c r="X40" t="n">
-        <v>260.5188500324821</v>
+        <v>260.5188500324822</v>
       </c>
       <c r="Y40" t="n">
-        <v>260.5188500324821</v>
+        <v>260.5188500324822</v>
       </c>
     </row>
     <row r="41">
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1334.161728122848</v>
+        <v>388.9026125057032</v>
       </c>
       <c r="C41" t="n">
-        <v>978.126800604672</v>
+        <v>388.9026125057032</v>
       </c>
       <c r="D41" t="n">
-        <v>661.622602887652</v>
+        <v>388.9026125057032</v>
       </c>
       <c r="E41" t="n">
-        <v>661.622602887652</v>
+        <v>388.9026125057032</v>
       </c>
       <c r="F41" t="n">
-        <v>350.6229779300643</v>
+        <v>77.9029875481155</v>
       </c>
       <c r="G41" t="n">
-        <v>350.6229779300643</v>
+        <v>77.9029875481155</v>
       </c>
       <c r="H41" t="n">
-        <v>40.88</v>
+        <v>77.9029875481155</v>
       </c>
       <c r="I41" t="n">
         <v>40.88</v>
@@ -7405,22 +7405,22 @@
         <v>41.99305728469727</v>
       </c>
       <c r="K41" t="n">
-        <v>547.8830572846972</v>
+        <v>95.65642019927013</v>
       </c>
       <c r="L41" t="n">
-        <v>614.4572042193706</v>
+        <v>162.2305671339435</v>
       </c>
       <c r="M41" t="n">
-        <v>1120.347204219371</v>
+        <v>487.6826115735371</v>
       </c>
       <c r="N41" t="n">
-        <v>1626.237204219371</v>
+        <v>993.5726115735371</v>
       </c>
       <c r="O41" t="n">
-        <v>1627.772052235491</v>
+        <v>1499.462611573537</v>
       </c>
       <c r="P41" t="n">
-        <v>1688.153202192202</v>
+        <v>1559.843761530247</v>
       </c>
       <c r="Q41" t="n">
         <v>2044</v>
@@ -7429,25 +7429,25 @@
         <v>1915.605384666613</v>
       </c>
       <c r="S41" t="n">
-        <v>1723.049923027469</v>
+        <v>1523.547086140334</v>
       </c>
       <c r="T41" t="n">
-        <v>1723.049923027469</v>
+        <v>1523.547086140334</v>
       </c>
       <c r="U41" t="n">
-        <v>1723.049923027469</v>
+        <v>1523.547086140334</v>
       </c>
       <c r="V41" t="n">
-        <v>1723.049923027469</v>
+        <v>1007.385469978718</v>
       </c>
       <c r="W41" t="n">
-        <v>1723.049923027469</v>
+        <v>777.790807410324</v>
       </c>
       <c r="X41" t="n">
-        <v>1723.049923027469</v>
+        <v>777.790807410324</v>
       </c>
       <c r="Y41" t="n">
-        <v>1723.049923027469</v>
+        <v>777.790807410324</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>136.0605533182198</v>
+        <v>791.120501872579</v>
       </c>
       <c r="C42" t="n">
-        <v>40.88</v>
+        <v>524.3529135437716</v>
       </c>
       <c r="D42" t="n">
-        <v>40.88</v>
+        <v>524.3529135437716</v>
       </c>
       <c r="E42" t="n">
-        <v>40.88</v>
+        <v>276.199279986284</v>
       </c>
       <c r="F42" t="n">
-        <v>40.88</v>
+        <v>276.199279986284</v>
       </c>
       <c r="G42" t="n">
-        <v>40.88</v>
+        <v>276.199279986284</v>
       </c>
       <c r="H42" t="n">
         <v>40.88</v>
@@ -7481,22 +7481,22 @@
         <v>40.88</v>
       </c>
       <c r="J42" t="n">
-        <v>186.1621101752989</v>
+        <v>282.192110175299</v>
       </c>
       <c r="K42" t="n">
-        <v>458.9128128734559</v>
+        <v>554.942812873456</v>
       </c>
       <c r="L42" t="n">
-        <v>875.303224468656</v>
+        <v>971.3332244686561</v>
       </c>
       <c r="M42" t="n">
-        <v>1114.606066211515</v>
+        <v>1210.636066211515</v>
       </c>
       <c r="N42" t="n">
-        <v>1402.622360819084</v>
+        <v>1498.652360819084</v>
       </c>
       <c r="O42" t="n">
-        <v>1791.399342502803</v>
+        <v>1791.399342502802</v>
       </c>
       <c r="P42" t="n">
         <v>2043.061306972309</v>
@@ -7505,28 +7505,28 @@
         <v>1995.611544254653</v>
       </c>
       <c r="R42" t="n">
-        <v>1995.611544254653</v>
+        <v>1748.506534048762</v>
       </c>
       <c r="S42" t="n">
-        <v>1995.611544254653</v>
+        <v>1748.506534048762</v>
       </c>
       <c r="T42" t="n">
-        <v>1685.067336964235</v>
+        <v>1437.962326758344</v>
       </c>
       <c r="U42" t="n">
-        <v>1378.809397812532</v>
+        <v>1437.962326758344</v>
       </c>
       <c r="V42" t="n">
-        <v>1058.091552164532</v>
+        <v>1117.244481110344</v>
       </c>
       <c r="W42" t="n">
-        <v>1058.091552164532</v>
+        <v>1117.244481110344</v>
       </c>
       <c r="X42" t="n">
-        <v>731.9675729267663</v>
+        <v>791.120501872579</v>
       </c>
       <c r="Y42" t="n">
-        <v>426.5217216478426</v>
+        <v>791.120501872579</v>
       </c>
     </row>
     <row r="43">
@@ -7590,10 +7590,10 @@
         <v>115.3727304885169</v>
       </c>
       <c r="T43" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="U43" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="V43" t="n">
         <v>40.88</v>
@@ -7615,46 +7615,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="C44" t="n">
-        <v>1323.589561385887</v>
+        <v>1559.570457148437</v>
       </c>
       <c r="D44" t="n">
-        <v>1323.589561385887</v>
+        <v>1243.066259431417</v>
       </c>
       <c r="E44" t="n">
-        <v>1012.111491075919</v>
+        <v>1008.071087035515</v>
       </c>
       <c r="F44" t="n">
-        <v>700.1017651082302</v>
+        <v>697.0714620779272</v>
       </c>
       <c r="G44" t="n">
-        <v>389.6661674983818</v>
+        <v>387.6459654781798</v>
       </c>
       <c r="H44" t="n">
-        <v>78.91308855821651</v>
+        <v>77.9029875481155</v>
       </c>
       <c r="I44" t="n">
         <v>40.88</v>
       </c>
       <c r="J44" t="n">
-        <v>467.9947465049924</v>
+        <v>41.99305728469727</v>
       </c>
       <c r="K44" t="n">
-        <v>925.4636166227428</v>
+        <v>95.65642019927013</v>
       </c>
       <c r="L44" t="n">
-        <v>992.0377635574163</v>
+        <v>162.2305671339435</v>
       </c>
       <c r="M44" t="n">
-        <v>992.0377635574163</v>
+        <v>668.1205671339435</v>
       </c>
       <c r="N44" t="n">
-        <v>1497.927763557416</v>
+        <v>1052.418913514127</v>
       </c>
       <c r="O44" t="n">
-        <v>1499.462611573537</v>
+        <v>1053.953761530247</v>
       </c>
       <c r="P44" t="n">
         <v>1559.843761530247</v>
@@ -7663,28 +7663,28 @@
         <v>2044</v>
       </c>
       <c r="R44" t="n">
-        <v>1914.595283656512</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="S44" t="n">
-        <v>1914.595283656512</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="T44" t="n">
-        <v>1839.751177547504</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="U44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="V44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="W44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="X44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
       <c r="Y44" t="n">
-        <v>1323.589561385887</v>
+        <v>1915.605384666613</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1058.401150407082</v>
+        <v>1633.910250359403</v>
       </c>
       <c r="C45" t="n">
-        <v>790.6234610681739</v>
+        <v>1367.142662030595</v>
       </c>
       <c r="D45" t="n">
-        <v>536.1409490502924</v>
+        <v>1113.670251022815</v>
       </c>
       <c r="E45" t="n">
-        <v>286.9772144827039</v>
+        <v>865.5166174653273</v>
       </c>
       <c r="F45" t="n">
-        <v>40.88</v>
+        <v>620.4295039927243</v>
       </c>
       <c r="G45" t="n">
-        <v>40.88</v>
+        <v>389.609770785626</v>
       </c>
       <c r="H45" t="n">
-        <v>40.88</v>
+        <v>154.290490799342</v>
       </c>
       <c r="I45" t="n">
         <v>40.88</v>
       </c>
       <c r="J45" t="n">
-        <v>281.202110175299</v>
+        <v>282.192110175299</v>
       </c>
       <c r="K45" t="n">
-        <v>601.8837562696824</v>
+        <v>603.8637562696823</v>
       </c>
       <c r="L45" t="n">
-        <v>1017.284167864883</v>
+        <v>1020.254167864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1255.597009607742</v>
+        <v>1163.527009607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1447.58330421531</v>
+        <v>1402.622360819083</v>
       </c>
       <c r="O45" t="n">
-        <v>1786.953682125444</v>
+        <v>1791.399342502802</v>
       </c>
       <c r="P45" t="n">
-        <v>2037.625646594951</v>
+        <v>2043.061306972309</v>
       </c>
       <c r="Q45" t="n">
-        <v>1989.165782867194</v>
+        <v>1995.611544254653</v>
       </c>
       <c r="R45" t="n">
-        <v>1989.165782867194</v>
+        <v>1995.611544254653</v>
       </c>
       <c r="S45" t="n">
-        <v>1619.136489973647</v>
+        <v>1995.611544254653</v>
       </c>
       <c r="T45" t="n">
-        <v>1307.582181673128</v>
+        <v>1995.611544254653</v>
       </c>
       <c r="U45" t="n">
-        <v>1307.582181673128</v>
+        <v>1995.611544254653</v>
       </c>
       <c r="V45" t="n">
-        <v>1307.582181673128</v>
+        <v>1674.893698606653</v>
       </c>
       <c r="W45" t="n">
-        <v>1307.582181673128</v>
+        <v>1674.893698606653</v>
       </c>
       <c r="X45" t="n">
-        <v>1307.582181673128</v>
+        <v>1674.893698606653</v>
       </c>
       <c r="Y45" t="n">
-        <v>1307.582181673128</v>
+        <v>1674.893698606653</v>
       </c>
     </row>
     <row r="46">
@@ -7797,52 +7797,52 @@
         <v>40.88</v>
       </c>
       <c r="J46" t="n">
-        <v>114.3827304885169</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="K46" t="n">
-        <v>114.3827304885169</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="L46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="M46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="N46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="O46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="P46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="Q46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="R46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="S46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="T46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="U46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="V46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="W46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="X46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
       <c r="Y46" t="n">
-        <v>40.88</v>
+        <v>115.3727304885169</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>13.1240997124269</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>648.7533869346734</v>
+        <v>204.6180495756453</v>
       </c>
       <c r="M2" t="n">
-        <v>714.1944596128085</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>401.2134002808905</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
         <v>714.4496484685648</v>
       </c>
       <c r="P2" t="n">
-        <v>655.0089394376664</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>141.0537677445708</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,13 +8204,13 @@
         <v>13.1240997124269</v>
       </c>
       <c r="K5" t="n">
-        <v>661.7945829145729</v>
+        <v>270.3143111095366</v>
       </c>
       <c r="L5" t="n">
         <v>648.7533869346734</v>
       </c>
       <c r="M5" t="n">
-        <v>668.7907737452958</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
@@ -8441,7 +8441,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>501.8870611704804</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>501.8870611704805</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>842.7942308769468</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>398.3752585961879</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,10 +8915,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>661.7945829145729</v>
       </c>
       <c r="L14" t="n">
-        <v>648.7533869346734</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>411.4164545760873</v>
+        <v>398.3752585961879</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>444.3177682411875</v>
+        <v>661.7945829145729</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>648.7533869346732</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>719.4799264057316</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>126.8053677445708</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,16 +9389,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>661.7945829145729</v>
+        <v>444.3177682411875</v>
       </c>
       <c r="L20" t="n">
-        <v>648.7533869346732</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>889.4908661501711</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>401.2134002808905</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>212.8279219127714</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>661.7945829145729</v>
@@ -9632,13 +9632,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>469.4373135719655</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>755.5706913252043</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>714.4496484685648</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9866,13 +9866,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>443.7533869346734</v>
+        <v>327.1890872964372</v>
       </c>
       <c r="M26" t="n">
         <v>980.4373135719657</v>
       </c>
       <c r="N26" t="n">
-        <v>795.649100642654</v>
+        <v>912.2134002808905</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>407.8843507102804</v>
+        <v>456.7945829145729</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>443.7533869346735</v>
       </c>
       <c r="M29" t="n">
         <v>980.4373135719657</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>553.4931907167643</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,10 +10340,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>443.7533869346734</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>863.8730139337292</v>
+        <v>980.4373135719657</v>
       </c>
       <c r="N32" t="n">
         <v>912.2134002808905</v>
@@ -10352,10 +10352,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>450.0089394376664</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>493.0322211283443</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>456.7945829145729</v>
+        <v>327.1890872964372</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>980.4373135719657</v>
       </c>
       <c r="N35" t="n">
-        <v>782.6079046627547</v>
+        <v>912.2134002808905</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>456.7945829145729</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>980.4373135719657</v>
       </c>
       <c r="N38" t="n">
-        <v>912.2134002808905</v>
+        <v>782.6079046627547</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>512.736423979854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,25 +11048,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>456.7945829145729</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>980.4373135719657</v>
+        <v>798.1767523998378</v>
       </c>
       <c r="N41" t="n">
         <v>912.2134002808905</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>509.4496484685648</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>486.2465776514379</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>407.8843507102804</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>469.4373135719655</v>
+        <v>980.4373135719657</v>
       </c>
       <c r="N44" t="n">
-        <v>912.2134002808905</v>
+        <v>789.3935481396613</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>450.0089394376664</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22712,13 +22712,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>244.4473521652717</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>309.833266425598</v>
+        <v>236.2731791343041</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>318.0074394565609</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22946,16 +22946,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>213.4277280134412</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>264.3294710987693</v>
       </c>
       <c r="Q7" t="n">
-        <v>236.2731791343109</v>
+        <v>76.52341947866049</v>
       </c>
       <c r="R7" t="n">
-        <v>318.0074394565609</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>309.833266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>244.4473521652748</v>
+        <v>244.4473521652766</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>273.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>241.4745782429939</v>
@@ -23232,16 +23232,16 @@
         <v>202.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>196.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>196.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>195.3312416337499</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>195.6455481507636</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,10 +23274,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>39.46192178219195</v>
+        <v>277.1377155410163</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>183.1454548540644</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>303.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23320,7 +23320,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2225690496970998</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23371,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.2225690496970287</v>
       </c>
     </row>
     <row r="13">
@@ -23387,19 +23387,19 @@
         <v>64.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>77.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>72.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>66.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>8.919141994927607</v>
+        <v>36.85272530054644</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>19.07165069178257</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>58.31290494868403</v>
+        <v>58.31290494868404</v>
       </c>
       <c r="L13" t="n">
         <v>187.129201928271</v>
@@ -23423,7 +23423,7 @@
         <v>405.4277280134412</v>
       </c>
       <c r="P13" t="n">
-        <v>456.3294710987693</v>
+        <v>192.4242582411139</v>
       </c>
       <c r="Q13" t="n">
         <v>501.833266425598</v>
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>137.4160648581299</v>
+        <v>267.9807946638317</v>
       </c>
       <c r="C14" t="n">
-        <v>240.4745782429939</v>
+        <v>241.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>201.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>195.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>195.8896287080119</v>
+        <v>196.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>194.3312416337499</v>
+        <v>195.3312416337499</v>
       </c>
       <c r="H14" t="n">
-        <v>194.6455481507636</v>
+        <v>195.6455481507636</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>277.1377155410163</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23560,7 +23560,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.2225690496822246</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54.86749039565481</v>
+        <v>79.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>63.72524664804467</v>
+        <v>64.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>76.53621805555548</v>
+        <v>77.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>71.98090483695654</v>
+        <v>72.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>65.38285596774193</v>
+        <v>66.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>35.85272530054642</v>
+        <v>36.85272530054644</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>57.31290494868403</v>
+        <v>58.31290494868404</v>
       </c>
       <c r="L16" t="n">
-        <v>186.129201928271</v>
+        <v>187.129201928271</v>
       </c>
       <c r="M16" t="n">
-        <v>281.6683655009106</v>
+        <v>282.6683655009106</v>
       </c>
       <c r="N16" t="n">
-        <v>332.934288386439</v>
+        <v>333.934288386439</v>
       </c>
       <c r="O16" t="n">
-        <v>404.4277280134412</v>
+        <v>160.5941658475684</v>
       </c>
       <c r="P16" t="n">
-        <v>455.3294710987693</v>
+        <v>456.3294710987693</v>
       </c>
       <c r="Q16" t="n">
-        <v>500.833266425598</v>
+        <v>501.833266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>509.0074394565609</v>
+        <v>510.0074394565609</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>151.0422993749866</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23684,10 +23684,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>38.44364543010755</v>
+        <v>39.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>79.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.348837760313998</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3488377603138701</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23885,28 +23885,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>90.12920192827096</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>185.6683655009106</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>236.934288386439</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>282.2548245966951</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>381.9792409557548</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>413.0074394565609</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>54.04229937498658</v>
+        <v>54.04229937498656</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23943,13 +23943,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3488377603140265</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.3488377603140221</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24122,16 +24122,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>90.12920192827096</v>
+        <v>90.12920192827097</v>
       </c>
       <c r="M22" t="n">
-        <v>185.6683655009106</v>
+        <v>185.6683655009105</v>
       </c>
       <c r="N22" t="n">
-        <v>210.7613849696929</v>
+        <v>236.934288386439</v>
       </c>
       <c r="O22" t="n">
-        <v>308.4277280134412</v>
+        <v>282.2548245966951</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>54.04229937498656</v>
+        <v>54.04229937498658</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3488377603140691</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3488377603138701</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24408,22 +24408,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>230.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>198.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>159.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>153.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>152.3312416337499</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,13 +24459,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>18.23680273164717</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>333.8101947938905</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>73.20668955891898</v>
       </c>
       <c r="V26" t="n">
         <v>378.8510241668239</v>
@@ -24502,10 +24502,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>70.54409597192739</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>78.96608718642113</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24535,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>149.5101831583486</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -24578,7 +24578,7 @@
         <v>29.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>23.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -24593,19 +24593,19 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>15.31290494868404</v>
+        <v>15.31290494868403</v>
       </c>
       <c r="L28" t="n">
         <v>144.129201928271</v>
       </c>
       <c r="M28" t="n">
-        <v>239.6683655009106</v>
+        <v>239.6683655009105</v>
       </c>
       <c r="N28" t="n">
         <v>290.934288386439</v>
       </c>
       <c r="O28" t="n">
-        <v>225.6338290155187</v>
+        <v>362.4277280134412</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>458.833266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>467.0074394565609</v>
+        <v>390.0617492758427</v>
       </c>
       <c r="S28" t="n">
         <v>108.0422993749866</v>
@@ -24635,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>36.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24651,16 +24651,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>131.89403364887</v>
       </c>
       <c r="G29" t="n">
-        <v>152.3312416337499</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24699,13 +24699,13 @@
         <v>234.1377155410164</v>
       </c>
       <c r="T29" t="n">
-        <v>333.8101947938905</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>398.1872060963494</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>46.0730037143602</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>387.3734759809475</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24733,10 +24733,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>60.87394082047167</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24781,13 +24781,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>149.1953597601868</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.3148233981618205</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24833,13 +24833,13 @@
         <v>15.31290494868403</v>
       </c>
       <c r="L31" t="n">
-        <v>124.6084857189287</v>
+        <v>144.129201928271</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>239.6683655009105</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>199.6441847153452</v>
       </c>
       <c r="O31" t="n">
         <v>362.4277280134412</v>
@@ -24848,7 +24848,7 @@
         <v>413.3294710987693</v>
       </c>
       <c r="Q31" t="n">
-        <v>458.833266425598</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>467.0074394565609</v>
@@ -24882,16 +24882,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>230.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>159.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>153.8896287080119</v>
@@ -24933,13 +24933,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>234.1377155410163</v>
+        <v>234.1377155410164</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>333.8101947938905</v>
       </c>
       <c r="U32" t="n">
-        <v>116.7323671814854</v>
+        <v>398.1872060963494</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -24948,7 +24948,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>126.9113028365325</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -25067,13 +25067,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>15.31290494868404</v>
+        <v>15.31290494868403</v>
       </c>
       <c r="L34" t="n">
         <v>144.129201928271</v>
       </c>
       <c r="M34" t="n">
-        <v>239.6683655009106</v>
+        <v>239.6683655009105</v>
       </c>
       <c r="N34" t="n">
         <v>290.934288386439</v>
@@ -25085,7 +25085,7 @@
         <v>413.3294710987693</v>
       </c>
       <c r="Q34" t="n">
-        <v>375.7173357854671</v>
+        <v>375.7173357854672</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25119,22 +25119,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>230.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>159.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>153.8896287080119</v>
+        <v>110.5963093579842</v>
       </c>
       <c r="G35" t="n">
-        <v>152.3312416337499</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25170,22 +25170,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>105.3284247769161</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>333.8101947938905</v>
       </c>
       <c r="U35" t="n">
-        <v>398.1872060963493</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25207,16 +25207,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>60.87394082047167</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>74.51153587502733</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>74.99864728332119</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25277,19 +25277,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -25304,13 +25304,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>15.31290494868403</v>
       </c>
       <c r="L37" t="n">
         <v>144.129201928271</v>
       </c>
       <c r="M37" t="n">
-        <v>239.6683655009106</v>
+        <v>239.6683655009105</v>
       </c>
       <c r="N37" t="n">
         <v>290.934288386439</v>
@@ -25319,16 +25319,16 @@
         <v>362.4277280134412</v>
       </c>
       <c r="P37" t="n">
-        <v>413.3294710987693</v>
+        <v>322.0393674276755</v>
       </c>
       <c r="Q37" t="n">
-        <v>458.833266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>222.4436523783793</v>
+        <v>467.0074394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>108.0422993749866</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25346,7 +25346,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="38">
@@ -25359,22 +25359,22 @@
         <v>230.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>68.72715913641829</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>152.3312416337499</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>152.6455481507636</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,13 +25407,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>234.1377155410163</v>
       </c>
       <c r="T38" t="n">
-        <v>333.8101947938905</v>
+        <v>333.8101947938906</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>340.0026336362625</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25450,7 +25450,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>70.5440959719274</v>
+        <v>70.54409597192739</v>
       </c>
       <c r="H39" t="n">
         <v>78.96608718642113</v>
@@ -25514,7 +25514,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7.362200714142713</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C40" t="n">
         <v>21.72524664804467</v>
@@ -25541,22 +25541,22 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>15.31290494868403</v>
+        <v>15.31290494868404</v>
       </c>
       <c r="L40" t="n">
         <v>144.129201928271</v>
       </c>
       <c r="M40" t="n">
-        <v>239.6683655009105</v>
+        <v>239.6683655009106</v>
       </c>
       <c r="N40" t="n">
         <v>290.934288386439</v>
       </c>
       <c r="O40" t="n">
-        <v>362.4277280134412</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>225.6338290155187</v>
       </c>
       <c r="Q40" t="n">
         <v>458.833266425598</v>
@@ -25565,7 +25565,7 @@
         <v>467.0074394565609</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>108.0422993749866</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,10 +25596,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>352.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>313.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>307.3632896068686</v>
@@ -25611,10 +25611,10 @@
         <v>306.3312416337499</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>306.6455481507636</v>
       </c>
       <c r="I41" t="n">
-        <v>36.65275767263435</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>197.5078085182637</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>487.8101947938905</v>
@@ -25653,10 +25653,10 @@
         <v>552.1872060963493</v>
       </c>
       <c r="V41" t="n">
-        <v>532.8510241668239</v>
+        <v>21.85102416682389</v>
       </c>
       <c r="W41" t="n">
-        <v>541.3734759809475</v>
+        <v>314.0747600382379</v>
       </c>
       <c r="X41" t="n">
         <v>495.2818334606677</v>
@@ -25672,16 +25672,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>287.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>169.8711646604817</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>250.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>245.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>242.6362423378769</v>
@@ -25690,7 +25690,7 @@
         <v>228.5115358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>232.9660871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>112.2763858913485</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>436.1177972923793</v>
+        <v>191.4838371885473</v>
       </c>
       <c r="S42" t="n">
         <v>365.3289999646113</v>
@@ -25729,7 +25729,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>303.1953597601868</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -25741,7 +25741,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>302.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25805,13 +25805,13 @@
         <v>262.0422993749866</v>
       </c>
       <c r="T43" t="n">
-        <v>38.46004201115059</v>
+        <v>112.2078451947823</v>
       </c>
       <c r="U43" t="n">
         <v>53.94796504494974</v>
       </c>
       <c r="V43" t="n">
-        <v>102.1703102162162</v>
+        <v>28.42250703258448</v>
       </c>
       <c r="W43" t="n">
         <v>129.3728098387097</v>
@@ -25830,16 +25830,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>385.9993129555745</v>
+        <v>384.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>353.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>314.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>74.71806893492541</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>389.1377155410163</v>
+        <v>388.1377155410163</v>
       </c>
       <c r="T44" t="n">
-        <v>414.7145297459725</v>
+        <v>487.8101947938906</v>
       </c>
       <c r="U44" t="n">
-        <v>42.18720609634937</v>
+        <v>552.1872060963493</v>
       </c>
       <c r="V44" t="n">
-        <v>533.8510241668239</v>
+        <v>532.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>542.3734759809475</v>
+        <v>541.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>496.2818334606677</v>
+        <v>495.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>415.3174326828064</v>
+        <v>414.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.86733569294159</v>
+        <v>246.9829428815487</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -25924,13 +25924,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>229.5115358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>233.9660871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>113.2763858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,28 +25957,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>437.1177972923792</v>
+        <v>436.1177972923792</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>365.3289999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>307.4387652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>304.1953597601868</v>
+        <v>303.1953597601868</v>
       </c>
       <c r="V45" t="n">
-        <v>318.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>336.3731429098285</v>
+        <v>335.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>323.8627394453875</v>
+        <v>322.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>303.3913927661343</v>
+        <v>302.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -25988,76 +25988,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>191.1138003370787</v>
+        <v>116.3659971534469</v>
       </c>
       <c r="C46" t="n">
-        <v>176.7252466480447</v>
+        <v>175.7252466480447</v>
       </c>
       <c r="D46" t="n">
-        <v>189.5362180555555</v>
+        <v>188.5362180555555</v>
       </c>
       <c r="E46" t="n">
-        <v>184.9809048369565</v>
+        <v>183.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>178.3828559677419</v>
+        <v>177.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>148.8527253005464</v>
+        <v>147.8527253005464</v>
       </c>
       <c r="H46" t="n">
-        <v>131.0716506917826</v>
+        <v>130.0716506917826</v>
       </c>
       <c r="I46" t="n">
-        <v>74.8851277512658</v>
+        <v>73.8851277512658</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>170.312904948684</v>
+        <v>169.312904948684</v>
       </c>
       <c r="L46" t="n">
-        <v>226.3614987446392</v>
+        <v>298.129201928271</v>
       </c>
       <c r="M46" t="n">
-        <v>394.6683655009106</v>
+        <v>393.6683655009106</v>
       </c>
       <c r="N46" t="n">
-        <v>445.934288386439</v>
+        <v>444.934288386439</v>
       </c>
       <c r="O46" t="n">
-        <v>517.4277280134412</v>
+        <v>516.4277280134412</v>
       </c>
       <c r="P46" t="n">
-        <v>568.3294710987693</v>
+        <v>567.3294710987693</v>
       </c>
       <c r="Q46" t="n">
-        <v>613.833266425598</v>
+        <v>612.833266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>622.0074394565609</v>
+        <v>621.0074394565609</v>
       </c>
       <c r="S46" t="n">
-        <v>263.0422993749866</v>
+        <v>262.0422993749866</v>
       </c>
       <c r="T46" t="n">
-        <v>113.2078451947823</v>
+        <v>112.2078451947823</v>
       </c>
       <c r="U46" t="n">
-        <v>54.94796504494974</v>
+        <v>53.94796504494974</v>
       </c>
       <c r="V46" t="n">
-        <v>103.1703102162162</v>
+        <v>102.1703102162162</v>
       </c>
       <c r="W46" t="n">
-        <v>130.3728098387097</v>
+        <v>129.3728098387097</v>
       </c>
       <c r="X46" t="n">
-        <v>151.4436454301076</v>
+        <v>150.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>191.4653528494624</v>
+        <v>190.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3896884.329393069</v>
+        <v>3895773.375313251</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4671242.190225553</v>
+        <v>4670131.236145735</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5445600.051058035</v>
+        <v>5444489.096978217</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6219957.911890518</v>
+        <v>6218846.9578107</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6861616.045525793</v>
+        <v>6860505.091445975</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7535580.522595413</v>
+        <v>7534469.568515592</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8209544.999665031</v>
+        <v>8208434.045585211</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8883509.476734655</v>
+        <v>8882398.522654839</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9557473.953804286</v>
+        <v>9556362.999724474</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9995275.490329681</v>
+        <v>9994164.536249865</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10431328.22080508</v>
+        <v>10431966.07277526</v>
       </c>
     </row>
   </sheetData>
@@ -26281,13 +26281,13 @@
         <v>1208430.19686937</v>
       </c>
       <c r="F2" t="n">
-        <v>1210429.914213041</v>
+        <v>1208430.196869371</v>
       </c>
       <c r="G2" t="n">
+        <v>1393844.149498476</v>
+      </c>
+      <c r="H2" t="n">
         <v>1393844.149498477</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1393844.149498476</v>
       </c>
       <c r="I2" t="n">
         <v>1393844.149498476</v>
@@ -26311,7 +26311,7 @@
         <v>788042.7657456847</v>
       </c>
       <c r="P2" t="n">
-        <v>784894.9148556847</v>
+        <v>788042.7657456849</v>
       </c>
     </row>
     <row r="3">
@@ -26333,10 +26333,10 @@
         <v>166400</v>
       </c>
       <c r="F3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>76800</v>
+        <v>77600</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26348,10 +26348,10 @@
         <v>303072</v>
       </c>
       <c r="K3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>76800</v>
+        <v>77600</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>650739.8234626309</v>
+        <v>654868.4597792358</v>
       </c>
       <c r="C4" t="n">
-        <v>649007.0841111749</v>
+        <v>653135.7204277798</v>
       </c>
       <c r="D4" t="n">
-        <v>647271.9941906389</v>
+        <v>651400.6305072436</v>
       </c>
       <c r="E4" t="n">
-        <v>546172.2968627792</v>
+        <v>550257.7329672743</v>
       </c>
       <c r="F4" t="n">
-        <v>545821.6216038717</v>
+        <v>548912.4865000374</v>
       </c>
       <c r="G4" t="n">
-        <v>635570.1845868181</v>
+        <v>639655.6206913129</v>
       </c>
       <c r="H4" t="n">
-        <v>633841.4826149177</v>
+        <v>637926.9187194126</v>
       </c>
       <c r="I4" t="n">
-        <v>632110.367347006</v>
+        <v>636195.8034515008</v>
       </c>
       <c r="J4" t="n">
-        <v>544264.7496165959</v>
+        <v>547741.0701282619</v>
       </c>
       <c r="K4" t="n">
-        <v>542754.5224673534</v>
+        <v>546230.8429790194</v>
       </c>
       <c r="L4" t="n">
-        <v>541242.1495728072</v>
+        <v>544718.4700844733</v>
       </c>
       <c r="M4" t="n">
-        <v>539727.6150875567</v>
+        <v>543203.9355992228</v>
       </c>
       <c r="N4" t="n">
-        <v>538210.9029535612</v>
+        <v>541687.2234652272</v>
       </c>
       <c r="O4" t="n">
-        <v>331441.1863119038</v>
+        <v>334917.5068235697</v>
       </c>
       <c r="P4" t="n">
-        <v>329289.4391624863</v>
+        <v>334281.1917187655</v>
       </c>
     </row>
     <row r="5">
@@ -26437,7 +26437,7 @@
         <v>63329.95199999999</v>
       </c>
       <c r="F5" t="n">
-        <v>63414.02099999999</v>
+        <v>63329.95199999999</v>
       </c>
       <c r="G5" t="n">
         <v>71484.64499999999</v>
@@ -26467,7 +26467,7 @@
         <v>41534.293</v>
       </c>
       <c r="P5" t="n">
-        <v>41450.224</v>
+        <v>41534.293</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>316240.5702095853</v>
+        <v>312111.9338929804</v>
       </c>
       <c r="C6" t="n">
-        <v>673355.3095610411</v>
+        <v>669226.6732444364</v>
       </c>
       <c r="D6" t="n">
-        <v>675090.3994815773</v>
+        <v>670961.7631649727</v>
       </c>
       <c r="E6" t="n">
-        <v>432527.9480065904</v>
+        <v>428442.511902096</v>
       </c>
       <c r="F6" t="n">
-        <v>600394.271609169</v>
+        <v>596187.7583693331</v>
       </c>
       <c r="G6" t="n">
-        <v>609989.3199116588</v>
+        <v>605103.8838071635</v>
       </c>
       <c r="H6" t="n">
-        <v>688518.0218835582</v>
+        <v>684432.5857790642</v>
       </c>
       <c r="I6" t="n">
-        <v>690249.1371514699</v>
+        <v>686163.7010469753</v>
       </c>
       <c r="J6" t="n">
-        <v>311318.3901087251</v>
+        <v>307842.069597059</v>
       </c>
       <c r="K6" t="n">
-        <v>615100.6172579678</v>
+        <v>612424.2967463018</v>
       </c>
       <c r="L6" t="n">
-        <v>540612.9901525137</v>
+        <v>536336.6696408477</v>
       </c>
       <c r="M6" t="n">
-        <v>618927.5246377646</v>
+        <v>615451.2041260982</v>
       </c>
       <c r="N6" t="n">
-        <v>620444.2367717598</v>
+        <v>616967.916260094</v>
       </c>
       <c r="O6" t="n">
-        <v>415067.286433781</v>
+        <v>411590.965922115</v>
       </c>
       <c r="P6" t="n">
-        <v>414155.2516931984</v>
+        <v>412227.2810269193</v>
       </c>
     </row>
   </sheetData>
@@ -26767,7 +26767,7 @@
         <v>208</v>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G2" t="n">
         <v>305</v>
@@ -26797,7 +26797,7 @@
         <v>97</v>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -26984,25 +26984,25 @@
         <v>208</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>154</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -27216,10 +27216,10 @@
         <v>208</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27231,7 +27231,7 @@
         <v>154</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27433,25 +27433,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.45950694036742</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>400</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>270.3488377603144</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>133.6527576726344</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>224.1106691800533</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.5115358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>329.9660871864211</v>
+        <v>276.2567734408753</v>
       </c>
       <c r="I3" t="n">
         <v>209.2763858913485</v>
@@ -27566,16 +27566,16 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>400</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>367.7543563620965</v>
-      </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27606,16 +27606,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
+        <v>345.4382760960438</v>
+      </c>
+      <c r="H4" t="n">
         <v>400</v>
       </c>
-      <c r="H4" t="n">
-        <v>264.4010118623762</v>
-      </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>170.8851277512658</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>21.75481768836678</v>
       </c>
       <c r="K4" t="n">
         <v>266.312904948684</v>
@@ -27654,13 +27654,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27679,19 +27679,19 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>228.1122646130017</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>133.6527576726344</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,25 +27718,25 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>224.1106691800533</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>270.3488377603143</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.63088589280632</v>
+        <v>143.9752650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>315.0834360259335</v>
       </c>
     </row>
     <row r="7">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27840,25 +27840,25 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8527253005464</v>
+        <v>388.2707348171761</v>
       </c>
       <c r="H7" t="n">
+        <v>227.0716506917826</v>
+      </c>
+      <c r="I7" t="n">
+        <v>170.8851277512658</v>
+      </c>
+      <c r="J7" t="n">
         <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>199.234580753529</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.75481768836678</v>
       </c>
       <c r="K7" t="n">
         <v>266.312904948684</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.129201928271</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.0422993749866</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2078451947823</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9479650449497</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27913,7 +27913,7 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>228.1122646130014</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -27922,7 +27922,7 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
@@ -27955,13 +27955,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>224.1106691800533</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>4.001595432948648</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27986,19 +27986,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>234.6192525682128</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>300.2485999061259</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>325.5115358750273</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28077,7 +28077,7 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.8527253005464</v>
@@ -28092,10 +28092,10 @@
         <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>266.312904948684</v>
+        <v>366.6243161582555</v>
       </c>
       <c r="L10" t="n">
-        <v>395.129201928271</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.0422993749866</v>
+      </c>
+      <c r="T10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
-        <v>340.7896177334969</v>
-      </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9479650449497</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28256,7 +28256,7 @@
         <v>208</v>
       </c>
       <c r="M12" t="n">
-        <v>208</v>
+        <v>33.22551724347372</v>
       </c>
       <c r="N12" t="n">
         <v>208</v>
@@ -28265,7 +28265,7 @@
         <v>208</v>
       </c>
       <c r="P12" t="n">
-        <v>33.22551724347372</v>
+        <v>208</v>
       </c>
       <c r="Q12" t="n">
         <v>208</v>
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I14" t="n">
         <v>133.6527576726344</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
-        <v>10.12774053670626</v>
+        <v>208</v>
       </c>
       <c r="L15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M15" t="n">
-        <v>209</v>
+        <v>33.22551724348932</v>
       </c>
       <c r="N15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
@@ -28751,10 +28751,10 @@
         <v>305</v>
       </c>
       <c r="T18" t="n">
-        <v>167.425955293498</v>
+        <v>305</v>
       </c>
       <c r="U18" t="n">
-        <v>305</v>
+        <v>167.4259552934979</v>
       </c>
       <c r="V18" t="n">
         <v>305</v>
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>305</v>
+        <v>167.4259552934979</v>
       </c>
       <c r="C21" t="n">
         <v>305</v>
       </c>
       <c r="D21" t="n">
-        <v>167.425955293498</v>
+        <v>305</v>
       </c>
       <c r="E21" t="n">
         <v>305</v>
@@ -29180,7 +29180,7 @@
         <v>305</v>
       </c>
       <c r="E24" t="n">
-        <v>167.425955293498</v>
+        <v>305</v>
       </c>
       <c r="F24" t="n">
         <v>305</v>
@@ -29192,7 +29192,7 @@
         <v>305</v>
       </c>
       <c r="I24" t="n">
-        <v>209.2763858913485</v>
+        <v>71.70234118484659</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29429,28 +29429,28 @@
         <v>251</v>
       </c>
       <c r="I27" t="n">
+        <v>209.2763858913485</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>251</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>187.403624651313</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>197.3811067663382</v>
+        <v>175.5083455263022</v>
       </c>
       <c r="Q27" t="n">
         <v>251</v>
@@ -29669,25 +29669,25 @@
         <v>251</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>251</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
-        <v>133.784731417651</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>133.7847314176512</v>
       </c>
       <c r="Q30" t="n">
         <v>251</v>
@@ -29906,22 +29906,22 @@
         <v>251</v>
       </c>
       <c r="J33" t="n">
-        <v>133.7847314176509</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>133.7847314176507</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -30143,7 +30143,7 @@
         <v>251</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>133.7847314176511</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30152,16 +30152,16 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>169.4887533203973</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>215.2959780972536</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="Q36" t="n">
         <v>251</v>
@@ -30617,7 +30617,7 @@
         <v>97</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K42" t="n">
         <v>47.58490566037736</v>
@@ -30632,7 +30632,7 @@
         <v>97</v>
       </c>
       <c r="O42" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>97</v>
@@ -30751,28 +30751,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y44" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45">
@@ -30830,76 +30830,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M45" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>47.58490566037736</v>
       </c>
       <c r="O45" t="n">
-        <v>47.09433962264151</v>
+        <v>97</v>
       </c>
       <c r="P45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y46" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -34746,7 +34746,7 @@
         <v>716</v>
       </c>
       <c r="K2" t="n">
-        <v>716</v>
+        <v>715.9999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>716</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34892,16 +34892,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1472746994536</v>
+        <v>100.5855507954974</v>
       </c>
       <c r="H4" t="n">
-        <v>37.32936117059359</v>
+        <v>172.9283493082174</v>
       </c>
       <c r="I4" t="n">
-        <v>229.1148722487342</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>378.2451823116332</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34940,13 +34940,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35126,25 +35126,25 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>143.4180095166296</v>
       </c>
       <c r="H7" t="n">
-        <v>172.9283493082174</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>28.34945300226317</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>378.2451823116332</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.870798071729041</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.95770062501344</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7921548052177</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0520349550503</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35363,7 +35363,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35378,10 +35378,10 @@
         <v>378.2451823116332</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>100.3114112095714</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.870798071729041</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.95770062501344</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>131.5817725387146</v>
+        <v>190.7921548052177</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0520349550503</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
         <v>67.24661306532676</v>
       </c>
       <c r="M11" t="n">
-        <v>373.3569173049812</v>
+        <v>590.8337319783669</v>
       </c>
       <c r="N11" t="n">
         <v>695.4500222078975</v>
@@ -35475,7 +35475,7 @@
         <v>60.99106056233367</v>
       </c>
       <c r="Q11" t="n">
-        <v>489.0467055250028</v>
+        <v>271.5698908516171</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35542,16 +35542,16 @@
         <v>531.596375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>352.7200421645043</v>
+        <v>177.945559407978</v>
       </c>
       <c r="N12" t="n">
-        <v>401.9255501086549</v>
+        <v>401.9255501086548</v>
       </c>
       <c r="O12" t="n">
         <v>503.7040219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>190.4295217581269</v>
+        <v>365.2040045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>64.02473490952042</v>
@@ -35609,7 +35609,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>37.11487224873419</v>
+        <v>37.1148722487342</v>
       </c>
       <c r="J13" t="n">
         <v>186.2451823116332</v>
@@ -35694,10 +35694,10 @@
         <v>431.4290368737297</v>
       </c>
       <c r="K14" t="n">
-        <v>54.20541708542714</v>
+        <v>716</v>
       </c>
       <c r="L14" t="n">
-        <v>716</v>
+        <v>67.24661306532676</v>
       </c>
       <c r="M14" t="n">
         <v>590.8337319783669</v>
@@ -35712,7 +35712,7 @@
         <v>60.99106056233367</v>
       </c>
       <c r="Q14" t="n">
-        <v>284.6110868315165</v>
+        <v>271.5698908516171</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,28 +35770,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>355.7496062376757</v>
+        <v>354.7496062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>238.0485951774975</v>
+        <v>435.9208546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>532.596375348687</v>
+        <v>531.596375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>353.7200421645043</v>
+        <v>177.9455594079936</v>
       </c>
       <c r="N15" t="n">
-        <v>402.9255501086549</v>
+        <v>401.9255501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>504.7040219027464</v>
+        <v>503.7040219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>366.2040045146532</v>
+        <v>365.2040045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>65.02473490952042</v>
+        <v>64.02473490952042</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35846,10 +35846,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>38.11487224873419</v>
+        <v>37.1148722487342</v>
       </c>
       <c r="J16" t="n">
-        <v>187.2451823116332</v>
+        <v>186.2451823116332</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>58.05203495505026</v>
+        <v>57.05203495505026</v>
       </c>
       <c r="V16" t="n">
-        <v>9.829689783783806</v>
+        <v>8.829689783783806</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -35931,16 +35931,16 @@
         <v>431.4290368737297</v>
       </c>
       <c r="K17" t="n">
-        <v>498.5231853266147</v>
+        <v>716</v>
       </c>
       <c r="L17" t="n">
-        <v>67.24661306532664</v>
+        <v>716</v>
       </c>
       <c r="M17" t="n">
         <v>590.8337319783669</v>
       </c>
       <c r="N17" t="n">
-        <v>695.4500222078975</v>
+        <v>318.2665261248411</v>
       </c>
       <c r="O17" t="n">
         <v>1.550351531435197</v>
@@ -35949,7 +35949,7 @@
         <v>60.99106056233367</v>
       </c>
       <c r="Q17" t="n">
-        <v>489.0467055250028</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36077,10 +36077,10 @@
         <v>30.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>60.14727469945358</v>
+        <v>60.14727469945356</v>
       </c>
       <c r="H19" t="n">
-        <v>77.92834930821745</v>
+        <v>77.92834930821743</v>
       </c>
       <c r="I19" t="n">
         <v>134.1148722487342</v>
@@ -36089,7 +36089,7 @@
         <v>283.2451823116332</v>
       </c>
       <c r="K19" t="n">
-        <v>38.68709505131597</v>
+        <v>38.68709505131596</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>95.79215480521769</v>
+        <v>95.79215480521771</v>
       </c>
       <c r="U19" t="n">
         <v>154.0520349550503</v>
@@ -36168,16 +36168,16 @@
         <v>431.4290368737297</v>
       </c>
       <c r="K20" t="n">
-        <v>716</v>
+        <v>498.5231853266147</v>
       </c>
       <c r="L20" t="n">
-        <v>716</v>
+        <v>67.24661306532664</v>
       </c>
       <c r="M20" t="n">
-        <v>420.0535525782055</v>
+        <v>590.8337319783669</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>695.4500222078975</v>
       </c>
       <c r="O20" t="n">
         <v>1.550351531435197</v>
@@ -36314,10 +36314,10 @@
         <v>30.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>60.14727469945356</v>
+        <v>60.14727469945358</v>
       </c>
       <c r="H22" t="n">
-        <v>77.92834930821743</v>
+        <v>77.92834930821745</v>
       </c>
       <c r="I22" t="n">
         <v>134.1148722487342</v>
@@ -36326,7 +36326,7 @@
         <v>283.2451823116332</v>
       </c>
       <c r="K22" t="n">
-        <v>38.68709505131596</v>
+        <v>38.68709505131597</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>95.79215480521771</v>
+        <v>95.79215480521769</v>
       </c>
       <c r="U22" t="n">
         <v>154.0520349550503</v>
@@ -36402,22 +36402,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>213.9522222003444</v>
+        <v>431.4290368737297</v>
       </c>
       <c r="K23" t="n">
         <v>716</v>
       </c>
       <c r="L23" t="n">
-        <v>67.24661306532664</v>
+        <v>67.24661306532676</v>
       </c>
       <c r="M23" t="n">
-        <v>590.8337319783669</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>695.4500222078975</v>
+        <v>354.3572910443138</v>
       </c>
       <c r="O23" t="n">
-        <v>1.550351531435197</v>
+        <v>716</v>
       </c>
       <c r="P23" t="n">
         <v>60.99106056233367</v>
@@ -36645,13 +36645,13 @@
         <v>54.20541708542714</v>
       </c>
       <c r="L26" t="n">
-        <v>511</v>
+        <v>394.4357003617638</v>
       </c>
       <c r="M26" t="n">
         <v>511</v>
       </c>
       <c r="N26" t="n">
-        <v>394.4357003617636</v>
+        <v>511</v>
       </c>
       <c r="O26" t="n">
         <v>1.550351531435197</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>41.72361410865146</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>146.7496062376757</v>
@@ -36724,19 +36724,19 @@
         <v>227.9208546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>511</v>
+        <v>323.596375348687</v>
       </c>
       <c r="M27" t="n">
         <v>144.7200421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>193.9255501086548</v>
+        <v>444.9255501086549</v>
       </c>
       <c r="O27" t="n">
         <v>295.7040219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>354.5851112809914</v>
+        <v>332.7123500409554</v>
       </c>
       <c r="Q27" t="n">
         <v>107.0247349095204</v>
@@ -36788,13 +36788,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>6.147274699453561</v>
+        <v>6.147274699453575</v>
       </c>
       <c r="H28" t="n">
-        <v>23.92834930821743</v>
+        <v>23.92834930821745</v>
       </c>
       <c r="I28" t="n">
-        <v>80.1148722487342</v>
+        <v>80.11487224873419</v>
       </c>
       <c r="J28" t="n">
         <v>229.2451823116332</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>41.79215480521771</v>
+        <v>41.7921548052177</v>
       </c>
       <c r="U28" t="n">
         <v>100.0520349550503</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>431.4290368737297</v>
+        <v>1.124300287572993</v>
       </c>
       <c r="K29" t="n">
-        <v>462.0897677957076</v>
+        <v>511</v>
       </c>
       <c r="L29" t="n">
-        <v>67.24661306532664</v>
+        <v>511.0000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>511</v>
@@ -36897,7 +36897,7 @@
         <v>60.99106056233367</v>
       </c>
       <c r="Q29" t="n">
-        <v>489.0467055250028</v>
+        <v>426.6878229721934</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,7 +36955,7 @@
         <v>41.72361410865147</v>
       </c>
       <c r="J30" t="n">
-        <v>397.7496062376757</v>
+        <v>146.7496062376757</v>
       </c>
       <c r="K30" t="n">
         <v>227.9208546407913</v>
@@ -36964,16 +36964,16 @@
         <v>323.596375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>144.7200421645043</v>
+        <v>395.7200421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>327.7102815263058</v>
+        <v>193.9255501086548</v>
       </c>
       <c r="O30" t="n">
         <v>295.7040219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>157.2040045146532</v>
+        <v>290.9887359323043</v>
       </c>
       <c r="Q30" t="n">
         <v>107.0247349095204</v>
@@ -37119,10 +37119,10 @@
         <v>54.20541708542714</v>
       </c>
       <c r="L32" t="n">
+        <v>67.24661306532664</v>
+      </c>
+      <c r="M32" t="n">
         <v>511</v>
-      </c>
-      <c r="M32" t="n">
-        <v>394.4357003617637</v>
       </c>
       <c r="N32" t="n">
         <v>511</v>
@@ -37131,10 +37131,10 @@
         <v>1.550351531435197</v>
       </c>
       <c r="P32" t="n">
-        <v>60.99106056233367</v>
+        <v>511</v>
       </c>
       <c r="Q32" t="n">
-        <v>489.0467055250028</v>
+        <v>366.2268533837735</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,25 +37189,25 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>41.72361410865146</v>
+        <v>41.72361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>280.5343376553266</v>
+        <v>146.7496062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>227.9208546407913</v>
+        <v>478.9208546407913</v>
       </c>
       <c r="L33" t="n">
         <v>323.596375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>395.7200421645043</v>
+        <v>144.7200421645043</v>
       </c>
       <c r="N33" t="n">
         <v>193.9255501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>295.7040219027464</v>
+        <v>429.4887533203971</v>
       </c>
       <c r="P33" t="n">
         <v>157.2040045146532</v>
@@ -37262,13 +37262,13 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>6.147274699453561</v>
+        <v>6.147274699453575</v>
       </c>
       <c r="H34" t="n">
-        <v>23.92834930821743</v>
+        <v>23.92834930821745</v>
       </c>
       <c r="I34" t="n">
-        <v>80.1148722487342</v>
+        <v>80.11487224873419</v>
       </c>
       <c r="J34" t="n">
         <v>229.2451823116332</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>41.79215480521771</v>
+        <v>41.7921548052177</v>
       </c>
       <c r="U34" t="n">
         <v>100.0520349550503</v>
@@ -37353,7 +37353,7 @@
         <v>1.124300287572993</v>
       </c>
       <c r="K35" t="n">
-        <v>511</v>
+        <v>381.3945043818643</v>
       </c>
       <c r="L35" t="n">
         <v>67.24661306532664</v>
@@ -37362,7 +37362,7 @@
         <v>511</v>
       </c>
       <c r="N35" t="n">
-        <v>381.3945043818642</v>
+        <v>511</v>
       </c>
       <c r="O35" t="n">
         <v>1.550351531435197</v>
@@ -37426,10 +37426,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>41.72361410865146</v>
+        <v>41.72361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>146.7496062376757</v>
+        <v>280.5343376553268</v>
       </c>
       <c r="K36" t="n">
         <v>227.9208546407913</v>
@@ -37438,16 +37438,16 @@
         <v>323.596375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>314.2087954849016</v>
+        <v>144.7200421645043</v>
       </c>
       <c r="N36" t="n">
         <v>193.9255501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>511</v>
+        <v>295.7040219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>157.2040045146532</v>
+        <v>408.2040045146532</v>
       </c>
       <c r="Q36" t="n">
         <v>107.0247349095204</v>
@@ -37499,13 +37499,13 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>6.147274699453561</v>
+        <v>6.147274699453575</v>
       </c>
       <c r="H37" t="n">
-        <v>23.92834930821743</v>
+        <v>23.92834930821745</v>
       </c>
       <c r="I37" t="n">
-        <v>80.1148722487342</v>
+        <v>80.11487224873419</v>
       </c>
       <c r="J37" t="n">
         <v>229.2451823116332</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>41.79215480521771</v>
+        <v>41.7921548052177</v>
       </c>
       <c r="U37" t="n">
         <v>100.0520349550503</v>
@@ -37587,10 +37587,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>431.4290368737297</v>
+        <v>1.124300287572993</v>
       </c>
       <c r="K38" t="n">
-        <v>54.20541708542709</v>
+        <v>511</v>
       </c>
       <c r="L38" t="n">
         <v>67.24661306532664</v>
@@ -37599,7 +37599,7 @@
         <v>511</v>
       </c>
       <c r="N38" t="n">
-        <v>511</v>
+        <v>381.3945043818642</v>
       </c>
       <c r="O38" t="n">
         <v>1.550351531435197</v>
@@ -37608,7 +37608,7 @@
         <v>60.99106056233367</v>
       </c>
       <c r="Q38" t="n">
-        <v>385.9310562352832</v>
+        <v>489.0467055250028</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>41.72361410865147</v>
+        <v>41.72361410865146</v>
       </c>
       <c r="J39" t="n">
         <v>280.5343376553268</v>
@@ -37736,13 +37736,13 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>6.147274699453575</v>
+        <v>6.147274699453561</v>
       </c>
       <c r="H40" t="n">
-        <v>23.92834930821745</v>
+        <v>23.92834930821743</v>
       </c>
       <c r="I40" t="n">
-        <v>80.11487224873419</v>
+        <v>80.1148722487342</v>
       </c>
       <c r="J40" t="n">
         <v>229.2451823116332</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>41.7921548052177</v>
+        <v>41.79215480521771</v>
       </c>
       <c r="U40" t="n">
         <v>100.0520349550503</v>
@@ -37827,25 +37827,25 @@
         <v>1.124300287572993</v>
       </c>
       <c r="K41" t="n">
-        <v>511</v>
+        <v>54.20541708542714</v>
       </c>
       <c r="L41" t="n">
         <v>67.24661306532664</v>
       </c>
       <c r="M41" t="n">
-        <v>511</v>
+        <v>328.7394388278723</v>
       </c>
       <c r="N41" t="n">
         <v>511</v>
       </c>
       <c r="O41" t="n">
-        <v>1.550351531435197</v>
+        <v>511</v>
       </c>
       <c r="P41" t="n">
         <v>60.99106056233367</v>
       </c>
       <c r="Q41" t="n">
-        <v>359.441209906867</v>
+        <v>489.0467055250028</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>146.7496062376757</v>
+        <v>243.7496062376757</v>
       </c>
       <c r="K42" t="n">
         <v>275.5057603011687</v>
@@ -37918,7 +37918,7 @@
         <v>290.9255501086549</v>
       </c>
       <c r="O42" t="n">
-        <v>392.7040219027464</v>
+        <v>295.7040219027464</v>
       </c>
       <c r="P42" t="n">
         <v>254.2040045146532</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>431.4290368737297</v>
+        <v>1.124300287572993</v>
       </c>
       <c r="K44" t="n">
-        <v>462.0897677957076</v>
+        <v>54.20541708542714</v>
       </c>
       <c r="L44" t="n">
         <v>67.24661306532664</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="N44" t="n">
-        <v>511</v>
+        <v>388.1801478587709</v>
       </c>
       <c r="O44" t="n">
         <v>1.550351531435197</v>
       </c>
       <c r="P44" t="n">
-        <v>60.99106056233367</v>
+        <v>511</v>
       </c>
       <c r="Q44" t="n">
         <v>489.0467055250028</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>242.7496062376757</v>
+        <v>243.7496062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>323.9208546407913</v>
+        <v>324.9208546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>419.596375348687</v>
+        <v>420.596375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>240.7200421645043</v>
+        <v>144.7200421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>193.9255501086548</v>
+        <v>241.5104557690322</v>
       </c>
       <c r="O45" t="n">
-        <v>342.7983615253879</v>
+        <v>392.7040219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>253.2040045146532</v>
+        <v>254.2040045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>74.24518231163322</v>
+        <v>75.24518231163322</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
